--- a/Samsung_qty_H1_tags.xlsx
+++ b/Samsung_qty_H1_tags.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -658,41 +658,45 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>AH81-15059A</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>ah81-15059a</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Adaptor– Samsung Parts Usa - AH81-15059A</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Site title: samsung AH81-15059A ADAPTOR– Samsung Parts USA | Adaptor (samsungpartsusa.com)</t>
         </is>
       </c>
     </row>
@@ -768,7 +772,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -844,7 +848,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -878,7 +882,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -912,7 +916,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -946,7 +950,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1060,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>mentioned only in a collection-page summary as soundbar rear-left speaker assy $360.95; no exact product link returned; retry not done (budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1094,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>mentioned only in collection-page summary as laptop CPU heat sink $55.95; no exact product link returned; retry not done (budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1170,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1246,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>mentioned only in collection-page summary as soundbar Svc Jdm Screw $5.95; no exact product link returned; retry not done (budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1280,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1314,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1348,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1424,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1458,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1492,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1610,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in samsungparts.com-filtered search; fallback retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1644,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1678,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -1763,36 +1767,40 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>BA96-08370A</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>ba96-08370a</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>searched, no exact hit</t>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop LCD Subins– Samsung Parts Usa Assembly - BA96-08370A</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung BA96-08370A ASSEMBLY LCD SUBINS– Samsung Parts USA | laptop LCD sub-assembly</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1876,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1910,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1944,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -1983,70 +1991,78 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>BN39-01011E</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>bn39-01011e</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>searched, no exact hit</t>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Lan Cable– Samsung Parts Usa - BN39-01011E</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Site title: BN39-01011E Lan Cable– Samsung Parts USA | LAN cable for select Samsung TVs</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>AH85-01078A</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>ah85-01078a</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>searched, no exact hit</t>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Oem Assembly Na-Smps Power Boa– Samsung Parts Usa - AH85-01078A</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung AH85-01078A Oem Assembly Na-Smps Power Boa– Samsung Parts USA | NA-SMPS power board assembly</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2180,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2298,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -2400,41 +2416,45 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>BA83-01561A</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>ba83-01561a</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>searched, no exact hit</t>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Jdm-Screw-Machine– Samsung Parts Usa - BA83-01561A</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Site title: samsung BA83-01561A JDM-SCREW-MACHINE– Samsung Parts USA | JDM screw machine; fits select Samsung laptops</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2530,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2606,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2640,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2716,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2750,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2784,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2944,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2978,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3054,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3088,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3164,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -3178,41 +3198,45 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>BA96-08319B</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>ba96-08319b</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="n"/>
-      <c r="F75" s="2" t="n"/>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>searched, no exact hit</t>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop LCD Subins-Silver– Samsung Parts Usa Assembly - BA96-08319B</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung BA96-08319B ASSEMBLY LCD SUBINS-SILVER– Samsung Parts USA | laptop LCD assembly (subins, silver)</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3270,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3346,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3464,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>only sibling BA98-03666B found; retry found nothing</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -3655,36 +3679,40 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>AH91-09033F</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>ah91-09033f</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="n"/>
-      <c r="F87" s="2" t="n"/>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>retry found nothing</t>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n"/>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Speaker Assembly - AH91-09033F</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>Site title: AH91-09033F ASSEMBLY SPEAKER | Assembly speaker (soundbar/TV speaker); page notes no longer available with comparable replacement</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3746,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>retry found nothing</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3822,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>only sibling AH94-03880A found; retry found nothing</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3856,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>retry found nothing</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4134,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>retry found nothing</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -4220,41 +4248,45 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>BA98-01478A</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>ba98-01478a</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="n"/>
-      <c r="F102" s="2" t="n"/>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>searched, no exact hit</t>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="n"/>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Case-Lower Lcd– Samsung Parts Usa Assembly - BA98-01478A</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>Site title: BA98-01478A ASSEMBLY CASE-LOWER LCD– Samsung Parts USA | laptop lower LCD case assembly</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4404,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4438,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4514,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -4516,41 +4548,45 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>AH81-15944A</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t>ah81-15944a</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="n"/>
-      <c r="F110" s="2" t="n"/>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>searched, no exact hit</t>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n"/>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Service Jdm-Remocon– Samsung Parts Usa - AH81-15944A</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung AH81-15944A Service Jdm-Remocon– Samsung Parts USA | remote control (Service JDM-Remocon) for speakers/soundbars</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4620,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4654,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4688,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -4728,41 +4764,45 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
         <is>
           <t>AH81-15682A</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>ah81-15682a</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="n"/>
-      <c r="F116" s="2" t="n"/>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>searched, no exact hit</t>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="n"/>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Samsung Service Jdm-Sub W/F Ps-Wr45Bb|Samsung Parts Usa - AH81-15682A</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung samsung AH81-15682A SERVICE JDM-SUB W/F PS-WR45BB|Samsung Parts USA | service JDM sub woofer PS-WR45BB; speaker/soundbar; listed no longer available</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4836,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4870,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4904,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4938,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -4932,7 +4972,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -4966,7 +5006,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5082,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5116,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5150,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5184,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5218,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -5212,7 +5252,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5286,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5320,7 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -5411,36 +5451,44 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
         <is>
           <t>BA98-03038A</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>ba98-03038a</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="n"/>
-      <c r="F135" s="2" t="n"/>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>searched, no exact hit</t>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Verified (page found)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://samsungparts.com/products/ba98-03038a</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Rubber Foot Down Assembly - BA98-03038A</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Site title: Samsung BA98-03038A ASSEMBLY RUBBER FOOT DOWN | laptop assembly rubber foot down</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5522,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5682,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5842,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5960,7 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -5959,36 +6007,44 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
         <is>
           <t>6001-002610</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="C149" s="3" t="inlineStr">
         <is>
           <t>6001-002610</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="n"/>
-      <c r="F149" s="2" t="n"/>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>searched, no exact hit</t>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Verified (page found)</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>https://samsungparts.com/products/6001-002610</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Machine Screw - 6001-002610</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung 6001-002610 Screw-Machine | machine screw</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6204,7 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6238,7 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6272,7 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6306,7 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -6326,41 +6382,45 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
         <is>
           <t>AH81-13316A</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="C159" s="3" t="inlineStr">
         <is>
           <t>ah81-13316a</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="n"/>
-      <c r="F159" s="2" t="n"/>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>searched, no exact hit</t>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="n"/>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Service Jdm Antenna|Samsung Parts Usa - AH81-13316A</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung AH81-13316A Svc Jdm Antenna|Samsung Parts USA | Svc Jdm Antenna</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6580,7 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on first search or retry (neighbouring numbers only)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6732,7 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on first search or retry (neighbouring numbers only)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6846,7 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on first search or retry (neighbouring numbers only)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -6820,41 +6880,45 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on first search or retry (neighbouring numbers only)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
         <is>
           <t>BA97-12306A</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="C172" s="3" t="inlineStr">
         <is>
           <t>ba97-12306a</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E172" s="2" t="n"/>
-      <c r="F172" s="2" t="n"/>
-      <c r="G172" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>no exact hit on first search or retry (neighbouring numbers only)</t>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="n"/>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Assembly Case Front-Top– Samsung Parts Usa - BA97-12306A</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung BA97-12306A Assy Case Front-Top– Samsung Parts USA | Assy Case Front-Top (laptop case)</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6994,7 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on first search or retry (neighbouring numbers only)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -6964,7 +7028,7 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on first search or retry (neighbouring numbers only)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -7221,36 +7285,40 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
         <is>
           <t>BA98-03232B</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C182" s="3" t="inlineStr">
         <is>
           <t>ba98-03232b</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E182" s="2" t="n"/>
-      <c r="F182" s="2" t="n"/>
-      <c r="G182" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t>INCOMPLETE: first domain search had no exact hit; retry NOT run (web search budget exhausted)</t>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="n"/>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Case Rear|Samsung Parts Usa Assembly - BA98-03232B</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H182" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung BA98-03232B ASSEMBLY CASE REAR|Samsung Parts USA | Assembly case rear (laptop); page notes no longer available with comparable replacement</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7352,7 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>INCOMPLETE: first domain search had no exact hit; retry NOT run (web search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7386,7 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>INCOMPLETE: first domain search had no exact hit; retry NOT run (web search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7420,7 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>INCOMPLETE: first domain search had no exact hit; retry NOT run (web search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7496,7 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>INCOMPLETE: first domain search had no exact hit; retry NOT run (web search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -7504,7 +7572,7 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>INCOMPLETE: first domain search had no exact hit; retry NOT run (web search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7606,7 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7640,7 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7674,7 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7708,7 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7742,7 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -7708,7 +7776,7 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -7784,7 +7852,7 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7970,7 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -7978,7 +8046,7 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -8012,7 +8080,7 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -8059,36 +8127,40 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B205" s="2" t="inlineStr">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
         <is>
           <t>6001-002653</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr">
+      <c r="C205" s="3" t="inlineStr">
         <is>
           <t>6001-002653</t>
         </is>
       </c>
-      <c r="D205" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E205" s="2" t="n"/>
-      <c r="F205" s="2" t="n"/>
-      <c r="G205" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H205" s="2" t="inlineStr">
-        <is>
-          <t>searched, no exact hit</t>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="n"/>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Screw, M3 X 6– Samsung Parts Usa - 6001-002653</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H205" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 6001-002653 Screw, M3 x 6– Samsung Parts USA | M3 x 6 screw</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8194,7 @@
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8312,7 @@
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8346,7 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -8350,7 +8422,7 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8498,7 @@
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8574,7 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -8536,7 +8608,7 @@
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -8654,7 +8726,7 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -8688,7 +8760,7 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8794,7 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8828,7 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>searched, no exact hit</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -9332,7 +9404,7 @@
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9522,7 @@
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -9484,7 +9556,7 @@
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -9518,7 +9590,7 @@
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -9552,7 +9624,7 @@
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -9641,36 +9713,44 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B248" s="2" t="inlineStr">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
         <is>
           <t>BN39-01652V</t>
         </is>
       </c>
-      <c r="C248" s="2" t="inlineStr">
+      <c r="C248" t="inlineStr">
         <is>
           <t>bn39-01652v</t>
         </is>
       </c>
-      <c r="D248" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E248" s="2" t="n"/>
-      <c r="F248" s="2" t="n"/>
-      <c r="G248" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H248" s="2" t="inlineStr">
-        <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Verified (page found)</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>https://samsungparts.com/products/bn39-01652v</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Samsung TV Lead Connector - BN39-01652V</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Site title: Samsung BN39-01652V Lead Connector | Lead connector for LED TVs; listed no longer available, comparable part suggested</t>
         </is>
       </c>
     </row>
@@ -9704,7 +9784,7 @@
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -9738,7 +9818,7 @@
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>search summary mentioned a battery assembly listing but no link URL returned; retry not done</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9852,7 @@
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -9861,36 +9941,40 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B254" s="2" t="inlineStr">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
         <is>
           <t>3404-001490</t>
         </is>
       </c>
-      <c r="C254" s="2" t="inlineStr">
+      <c r="C254" s="3" t="inlineStr">
         <is>
           <t>3404-001490</t>
         </is>
       </c>
-      <c r="D254" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E254" s="2" t="n"/>
-      <c r="F254" s="2" t="n"/>
-      <c r="G254" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H254" s="2" t="inlineStr">
-        <is>
-          <t>search summary mentioned Switch-Tact listing but no link URL returned; retry not done</t>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="n"/>
+      <c r="F254" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Vacuum Switch-Tact– Samsung Parts Usa - 3404-001490</t>
+        </is>
+      </c>
+      <c r="G254" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H254" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 3404-001490 SWITCH-TACT– Samsung Parts USA | Switch-Tact; listed under television parts (page text also mentions vacuum cleaner models)</t>
         </is>
       </c>
     </row>
@@ -9924,7 +10008,7 @@
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -9958,7 +10042,7 @@
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -9992,41 +10076,45 @@
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B258" s="2" t="inlineStr">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
         <is>
           <t>BN39-02207C</t>
         </is>
       </c>
-      <c r="C258" s="2" t="inlineStr">
+      <c r="C258" s="3" t="inlineStr">
         <is>
           <t>bn39-02207c</t>
         </is>
       </c>
-      <c r="D258" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E258" s="2" t="n"/>
-      <c r="F258" s="2" t="n"/>
-      <c r="G258" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H258" s="2" t="inlineStr">
-        <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="n"/>
+      <c r="F258" s="3" t="inlineStr">
+        <is>
+          <t>Samsung TV Lead Connector-Power– Samsung Parts Usa - BN39-02207C</t>
+        </is>
+      </c>
+      <c r="G258" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H258" s="3" t="inlineStr">
+        <is>
+          <t>Site title: BN39-02207C LEAD CONNECTOR-POWER– Samsung Parts USA | Lead Connector-Power (TV)</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10148,7 @@
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -10094,7 +10182,7 @@
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -10128,7 +10216,7 @@
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -10162,7 +10250,7 @@
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -10196,7 +10284,7 @@
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -10230,7 +10318,7 @@
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10352,7 @@
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10386,7 @@
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -10332,41 +10420,49 @@
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B268" s="2" t="inlineStr">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
         <is>
           <t>BA31-00117A</t>
         </is>
       </c>
-      <c r="C268" s="2" t="inlineStr">
+      <c r="C268" t="inlineStr">
         <is>
           <t>ba31-00117a</t>
         </is>
       </c>
-      <c r="D268" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E268" s="2" t="n"/>
-      <c r="F268" s="2" t="n"/>
-      <c r="G268" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H268" s="2" t="inlineStr">
-        <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Verified (page found)</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>https://samsungparts.com/products/ba31-00117a</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Samsung Laptop CPU Fan - BA31-00117A</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Site title: Samsung BA31-00117A Fan-Cpu | Laptop CPU cooling fan; listed no longer available, comparable part suggested</t>
         </is>
       </c>
     </row>
@@ -10400,7 +10496,7 @@
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10614,7 @@
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -10552,7 +10648,7 @@
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>only category-page mention, no product link; retry not done</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -10586,7 +10682,7 @@
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>no exact hit in domain search; retry not done (search budget exhausted)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -12218,7 +12314,7 @@
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12348,7 @@
       </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -12286,7 +12382,7 @@
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -12320,7 +12416,7 @@
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12450,7 @@
       </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -12388,7 +12484,7 @@
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -12422,7 +12518,7 @@
       </c>
       <c r="H324" s="2" t="inlineStr">
         <is>
-          <t>search showed collection page 'new-collection?page=244' naming 'Samsung AH81-15342A Service Jdm-Cable-Ffc' only; no products/ URL; retry not run (budget)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -12456,41 +12552,45 @@
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B326" s="2" t="inlineStr">
+      <c r="A326" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="inlineStr">
         <is>
           <t>BA44-00298A</t>
         </is>
       </c>
-      <c r="C326" s="2" t="inlineStr">
+      <c r="C326" s="3" t="inlineStr">
         <is>
           <t>ba44-00298a</t>
         </is>
       </c>
-      <c r="D326" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E326" s="2" t="n"/>
-      <c r="F326" s="2" t="n"/>
-      <c r="G326" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H326" s="2" t="inlineStr">
-        <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+      <c r="D326" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="n"/>
+      <c r="F326" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Samsung AC Adapter|Samsung Parts Usa - BA44-00298A</t>
+        </is>
+      </c>
+      <c r="G326" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H326" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung samsung BA44-00298A AC ADAPTER|Samsung Parts USA | AC adapter for Samsung computer/laptop; listed as discontinued</t>
         </is>
       </c>
     </row>
@@ -12524,7 +12624,7 @@
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -12558,41 +12658,45 @@
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B329" s="2" t="inlineStr">
+      <c r="A329" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B329" s="3" t="inlineStr">
         <is>
           <t>AH94-03759A</t>
         </is>
       </c>
-      <c r="C329" s="2" t="inlineStr">
+      <c r="C329" s="3" t="inlineStr">
         <is>
           <t>ah94-03759a</t>
         </is>
       </c>
-      <c r="D329" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E329" s="2" t="n"/>
-      <c r="F329" s="2" t="n"/>
-      <c r="G329" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H329" s="2" t="inlineStr">
-        <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+      <c r="D329" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E329" s="3" t="n"/>
+      <c r="F329" s="3" t="inlineStr">
+        <is>
+          <t>Samsung TV PCB Assembly|Samsung Parts Usa - AH94-03759A</t>
+        </is>
+      </c>
+      <c r="G329" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H329" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung AH94-03759A Pcb Assembly|Samsung Parts USA | PCB assembly for televisions; listed as no longer available</t>
         </is>
       </c>
     </row>
@@ -12626,41 +12730,45 @@
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B331" s="2" t="inlineStr">
+      <c r="A331" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B331" s="3" t="inlineStr">
         <is>
           <t>6001-001773</t>
         </is>
       </c>
-      <c r="C331" s="2" t="inlineStr">
+      <c r="C331" s="3" t="inlineStr">
         <is>
           <t>6001-001773</t>
         </is>
       </c>
-      <c r="D331" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E331" s="2" t="n"/>
-      <c r="F331" s="2" t="n"/>
-      <c r="G331" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H331" s="2" t="inlineStr">
-        <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+      <c r="D331" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E331" s="3" t="n"/>
+      <c r="F331" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Machine Washer Or Dryer Screw - 6001-001773</t>
+        </is>
+      </c>
+      <c r="G331" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H331" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Washer or Dryer 6001-001773 Screw-Machine | machine screw for Samsung washer/dryer</t>
         </is>
       </c>
     </row>
@@ -12778,7 +12886,7 @@
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -12812,7 +12920,7 @@
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -12888,7 +12996,7 @@
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -12922,7 +13030,7 @@
       </c>
       <c r="H338" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -12956,7 +13064,7 @@
       </c>
       <c r="H339" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -12990,7 +13098,7 @@
       </c>
       <c r="H340" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -13024,7 +13132,7 @@
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -13058,41 +13166,45 @@
       </c>
       <c r="H342" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B343" s="2" t="inlineStr">
+      <c r="A343" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B343" s="3" t="inlineStr">
         <is>
           <t>BA39-01262A</t>
         </is>
       </c>
-      <c r="C343" s="2" t="inlineStr">
+      <c r="C343" s="3" t="inlineStr">
         <is>
           <t>ba39-01262a</t>
         </is>
       </c>
-      <c r="D343" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E343" s="2" t="n"/>
-      <c r="F343" s="2" t="n"/>
-      <c r="G343" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="H343" s="2" t="inlineStr">
-        <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+      <c r="D343" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E343" s="3" t="n"/>
+      <c r="F343" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Cable– Samsung Parts Usa - BA39-01262A</t>
+        </is>
+      </c>
+      <c r="G343" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H343" s="3" t="inlineStr">
+        <is>
+          <t>Site title: BA39-01262A Cable– Samsung Parts USA | cable (BA39 laptop-family); OEM part</t>
         </is>
       </c>
     </row>
@@ -13168,7 +13280,7 @@
       </c>
       <c r="H345" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -13328,7 +13440,7 @@
       </c>
       <c r="H349" s="2" t="inlineStr">
         <is>
-          <t>samsungparts sitemap xml lists https://samsungparts.com/products/bn39-02709a but no titled product link returned; not counted; retry not run (budget)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -13404,7 +13516,7 @@
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13592,7 @@
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -13514,7 +13626,7 @@
       </c>
       <c r="H354" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -13590,7 +13702,7 @@
       </c>
       <c r="H356" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -13624,7 +13736,7 @@
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -13658,7 +13770,7 @@
       </c>
       <c r="H358" s="2" t="inlineStr">
         <is>
-          <t>sitemap xml lists products/bn39-02919a ('Lead Connector-Power;Qn65S95Ca') but no titled product link returned; not counted; retry not run (budget)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -13734,7 +13846,7 @@
       </c>
       <c r="H360" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -13768,7 +13880,7 @@
       </c>
       <c r="H361" s="2" t="inlineStr">
         <is>
-          <t>only seen as 'Trans Switching' on dvd-player-parts collection page, no products/ URL; retry not run (budget)</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>
@@ -13802,7 +13914,7 @@
       </c>
       <c r="H362" s="2" t="inlineStr">
         <is>
-          <t>no exact hit on samsungparts.com; retry (Samsung &lt;PN&gt;) not run, search budget exhausted</t>
+          <t>pass2 searched, no exact hit</t>
         </is>
       </c>
     </row>

--- a/Samsung_qty_H1_tags.xlsx
+++ b/Samsung_qty_H1_tags.xlsx
@@ -708,7 +708,7 @@
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Samsung Adaptor– Samsung Parts Usa - AH81-15059A</t>
+          <t>Samsung Adaptor - AH81-15059A</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1195,40 +1195,40 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>BA98-01912A</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>ba98-01912a</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA98-01912A</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | pass2 searched, no exact hit</t>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Case Upper (Joan-15,Se) Assembly - BA98-01912A</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Site title: BA98-01912A ASSEMBLY CASE UPPER;JOAN-15,SE | Assembly Case Upper (JOAN-15,SE) / fits laptop (Chromebook)</t>
         </is>
       </c>
     </row>
@@ -1545,40 +1545,40 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>BA92-18807A</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>ba92-18807a</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA92-18807A</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | pass2 searched, no exact hit</t>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Top Assembly Mother Board - BA92-18807A</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Site title: BA92-18807A Mother Bd-Top Assembly - Samsung Parts USA | Mother Bd-Top Assembly / fits laptop (Chromebook)</t>
         </is>
       </c>
     </row>
@@ -1667,40 +1667,40 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>AH94-00002U</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>ah94-00002u</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH94-00002U</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | pass2 searched, no exact hit</t>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Sub Amp PCB Assembly Amp - AH94-00002U</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ah94 00002u | PCB Assembly AMP-SUB AMP / fits speaker/soundbar</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Samsung Laptop LCD Subins– Samsung Parts Usa Assembly - BA96-08370A</t>
+          <t>Samsung Laptop LCD Subins Assembly - BA96-08370A</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2124,7 +2124,7 @@
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Samsung Lan Cable– Samsung Parts Usa - BN39-01011E</t>
+          <t>Samsung Lan Cable - BN39-01011E</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -2162,7 +2162,7 @@
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Samsung Oem Assembly Na-Smps Power Boa– Samsung Parts Usa - AH85-01078A</t>
+          <t>Samsung Smps Power Boa Oem Assembly Na - AH85-01078A</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -2383,40 +2383,44 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>BA98-01974A</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>ba98-01974a</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="n"/>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA98-01974A</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | pass2 searched, no exact hit</t>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Verified (page found)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://samsungparts.com/products/ba98-01974a</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Case Upper Assembly - BA98-01974A</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Site title: ba98 01974a | Assembly Case Upper;Joan-11,Se / fits laptop</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2570,7 @@
       <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Samsung Laptop Jdm-Screw-Machine– Samsung Parts Usa - BA83-01561A</t>
+          <t>Samsung Laptop Jdm-Screw-Machine - BA83-01561A</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -3217,40 +3221,40 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>BA98-03667A</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>ba98-03667a</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="n"/>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA98-03667A</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | pass2 searched, no exact hit</t>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Assembly Rubber Foot Front Left (Gummifuss Vorne L) - BA98-03667A</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>Site title: SAMSUNG BA98-03667A ASSY GUMMIFUSS VORNE L; MARS3-16 WIFI, S | Assy Rubber Foot Front Left (Gummifuss vorne L) / fits laptop (Galaxy Book3 Pro 360 / Book4 Pro 360)</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3400,7 @@
       <c r="E75" s="3" t="n"/>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Samsung Laptop LCD Subins-Silver– Samsung Parts Usa Assembly - BA96-08319B</t>
+          <t>Samsung Laptop Silver LCD Subins Assembly - BA96-08319B</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -4478,7 +4482,7 @@
       <c r="E102" s="3" t="n"/>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Samsung Laptop Case-Lower Lcd– Samsung Parts Usa Assembly - BA98-01478A</t>
+          <t>Samsung Laptop Lower LCD Case Assembly - BA98-01478A</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -4733,40 +4737,44 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
         <is>
           <t>BA92-17263A</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>ba92-17263a</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="n"/>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA92-17263A</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | pass2 searched, no exact hit</t>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Verified (page found)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://samsungparts.com/products/ba92-17263a</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Top Board Assembly WLAN - BA92-17263A</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Site title: ba92 17263a | Wlan-Top board assembly / fits laptop</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4802,7 @@
       <c r="E110" s="3" t="n"/>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>Samsung Soundbar Service Jdm-Remocon– Samsung Parts Usa - AH81-15944A</t>
+          <t>Samsung Soundbar Remote Control Service Jdm - AH81-15944A</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -4965,40 +4973,40 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
         <is>
           <t>AH81-11803A</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="C115" s="3" t="inlineStr">
         <is>
           <t>ah81-11803a</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="n"/>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-11803A</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | pass2 searched, no exact hit</t>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="n"/>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Bluetooth (Bt) Module - AH81-11803A</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>Site title: AH81-11803A A S Bt Module | A/S Bluetooth (BT) Module / fits speaker/soundbar</t>
         </is>
       </c>
     </row>
@@ -5155,40 +5163,40 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
         <is>
           <t>AH94-03659A</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C120" s="3" t="inlineStr">
         <is>
           <t>ah94-03659a</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="n"/>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH94-03659A</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | pass2 searched, no exact hit</t>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="n"/>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>Samsung PCB Board Assembly Power - AH94-03659A</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>Site title: AH94-03659A PCB Board Assembly POWER - Samsung Parts USA | PCB Board Assembly POWER / fits None</t>
         </is>
       </c>
     </row>
@@ -6557,40 +6565,44 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
         <is>
           <t>BA92-16947A</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>ba92-16947a</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="n"/>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA92-16947A</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | pass2 searched, no exact hit</t>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Verified (page found)</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://samsungparts.com/products/ba92-16947a</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Sub USB Assembly Board - BA92-16947A</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Site title: ba92 16947a | Board-Sub USB Assembly / fits laptop</t>
         </is>
       </c>
     </row>
@@ -7254,7 +7266,7 @@
       <c r="E172" s="3" t="n"/>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Samsung Laptop Assembly Case Front-Top– Samsung Parts Usa - BA97-12306A</t>
+          <t>Samsung Laptop Top Assembly Case Front - BA97-12306A</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -7913,40 +7925,40 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
         <is>
           <t>BA83-02135A</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C189" s="3" t="inlineStr">
         <is>
           <t>ba83-02135a</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E189" s="2" t="n"/>
-      <c r="F189" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA83-02135A</t>
-        </is>
-      </c>
-      <c r="G189" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H189" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | pass2 searched, no exact hit</t>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="n"/>
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Jdm-Gummifuss (German For Rubber Foot) - BA83-02135A</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H189" s="3" t="inlineStr">
+        <is>
+          <t>Site title: SAMSUNG BA83-02135A JDM-GUMMIFUSS;NP750XDAZ,HQ22290291000, | JDM-GUMMIFUSS (German for rubber foot) / fits laptop (Galaxy Book 15 NP750XDA/NP750XDAZ)</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8576,7 @@
       <c r="E205" s="3" t="n"/>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Samsung Screw, M3 X 6– Samsung Parts Usa - 6001-002653</t>
+          <t>Samsung Screw, M3 X 6 - 6001-002653</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -10277,40 +10289,44 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B249" s="2" t="inlineStr">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
         <is>
           <t>BA44-00312A</t>
         </is>
       </c>
-      <c r="C249" s="2" t="inlineStr">
+      <c r="C249" t="inlineStr">
         <is>
           <t>ba44-00312a</t>
         </is>
       </c>
-      <c r="D249" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E249" s="2" t="n"/>
-      <c r="F249" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA44-00312A</t>
-        </is>
-      </c>
-      <c r="G249" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H249" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | pass2 searched, no exact hit</t>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Verified (page found)</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>https://samsungparts.com/products/ba44-00312a</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Samsung Adaptor (Laptop AC Adapter) - BA44-00312A</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Site title: ba44 00312a | Adaptor (laptop AC adapter) / fits laptop</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10514,7 @@
       <c r="E254" s="3" t="n"/>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>Samsung Vacuum Switch-Tact– Samsung Parts Usa - 3404-001490</t>
+          <t>Samsung Vacuum Tact Switch - 3404-001490</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -10650,7 +10666,7 @@
       <c r="E258" s="3" t="n"/>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>Samsung TV Lead Connector-Power– Samsung Parts Usa - BN39-02207C</t>
+          <t>Samsung TV Power Lead Connector - BN39-02207C</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -10855,40 +10871,44 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B264" s="2" t="inlineStr">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
         <is>
           <t>BA98-01635A</t>
         </is>
       </c>
-      <c r="C264" s="2" t="inlineStr">
+      <c r="C264" t="inlineStr">
         <is>
           <t>ba98-01635a</t>
         </is>
       </c>
-      <c r="D264" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E264" s="2" t="n"/>
-      <c r="F264" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA98-01635A</t>
-        </is>
-      </c>
-      <c r="G264" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H264" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | pass2 searched, no exact hit</t>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Verified (page found)</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>https://samsungparts.com/products/ba98-01635a</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Case Front Assembly - BA98-01635A</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Site title: ba98 01635a | Assembly Case Front;Hopper-12 / fits Chromebook/laptop</t>
         </is>
       </c>
     </row>
@@ -12439,40 +12459,40 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B304" s="2" t="inlineStr">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
         <is>
           <t>BA98-04622A</t>
         </is>
       </c>
-      <c r="C304" s="2" t="inlineStr">
+      <c r="C304" s="3" t="inlineStr">
         <is>
           <t>ba98-04622a</t>
         </is>
       </c>
-      <c r="D304" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E304" s="2" t="n"/>
-      <c r="F304" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA98-04622A</t>
-        </is>
-      </c>
-      <c r="G304" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H304" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E304" s="3" t="n"/>
+      <c r="F304" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Case Rear Assembly - BA98-04622A</t>
+        </is>
+      </c>
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H304" s="3" t="inlineStr">
+        <is>
+          <t>Site title: samsung assembly case rear gb6 ultra 1 ba98 04622a | Assembly Case Rear / fits None</t>
         </is>
       </c>
     </row>
@@ -12740,7 +12760,7 @@
       <c r="E311" s="3" t="n"/>
       <c r="F311" s="3" t="inlineStr">
         <is>
-          <t>Samsung TV Remote Control– Samsung Parts Usa - AA59-00750A</t>
+          <t>Samsung TV Remote Control - AA59-00750A</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
@@ -13177,40 +13197,40 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B323" s="2" t="inlineStr">
+      <c r="A323" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
         <is>
           <t>BA41-02779A</t>
         </is>
       </c>
-      <c r="C323" s="2" t="inlineStr">
+      <c r="C323" s="3" t="inlineStr">
         <is>
           <t>ba41-02779a</t>
         </is>
       </c>
-      <c r="D323" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E323" s="2" t="n"/>
-      <c r="F323" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA41-02779A</t>
-        </is>
-      </c>
-      <c r="G323" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H323" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | pass2 searched, no exact hit</t>
+      <c r="D323" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="n"/>
+      <c r="F323" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Fpc (Fpc - BA41-02779A</t>
+        </is>
+      </c>
+      <c r="G323" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H323" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ba41 02779a | FPC (Fpc;Terra_Tp_Fpcfccll33Xw82) / fits None</t>
         </is>
       </c>
     </row>
@@ -13873,78 +13893,78 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B341" s="2" t="inlineStr">
+      <c r="A341" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B341" s="3" t="inlineStr">
         <is>
           <t>BA98-00861A</t>
         </is>
       </c>
-      <c r="C341" s="2" t="inlineStr">
+      <c r="C341" s="3" t="inlineStr">
         <is>
           <t>ba98-00861a</t>
         </is>
       </c>
-      <c r="D341" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E341" s="2" t="n"/>
-      <c r="F341" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA98-00861A</t>
-        </is>
-      </c>
-      <c r="G341" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H341" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | pass2 searched, no exact hit</t>
+      <c r="D341" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E341" s="3" t="n"/>
+      <c r="F341" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Hinge Extrusion Assembly Cover - BA98-00861A</t>
+        </is>
+      </c>
+      <c r="G341" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H341" s="3" t="inlineStr">
+        <is>
+          <t>Site title: BA98-00861A Cover -Hinge Extursion Assembly | Cover-Hinge Extrusion Assembly / fits laptop</t>
         </is>
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B342" s="2" t="inlineStr">
+      <c r="A342" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
         <is>
           <t>AH94-03616B</t>
         </is>
       </c>
-      <c r="C342" s="2" t="inlineStr">
+      <c r="C342" s="3" t="inlineStr">
         <is>
           <t>ah94-03616b</t>
         </is>
       </c>
-      <c r="D342" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E342" s="2" t="n"/>
-      <c r="F342" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH94-03616B</t>
-        </is>
-      </c>
-      <c r="G342" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H342" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | pass2 searched, no exact hit</t>
+      <c r="D342" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E342" s="3" t="n"/>
+      <c r="F342" s="3" t="inlineStr">
+        <is>
+          <t>Samsung PCB Board Assembly Front - AH94-03616B</t>
+        </is>
+      </c>
+      <c r="G342" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H342" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung SMGAH94-03616B PCB Board Assembly FRONT | PCB Board Assembly FRONT / fits None</t>
         </is>
       </c>
     </row>
@@ -13972,7 +13992,7 @@
       <c r="E343" s="3" t="n"/>
       <c r="F343" s="3" t="inlineStr">
         <is>
-          <t>Samsung Laptop Cable– Samsung Parts Usa - BA39-01262A</t>
+          <t>Samsung Laptop Cable - BA39-01262A</t>
         </is>
       </c>
       <c r="G343" s="3" t="inlineStr">
@@ -14825,40 +14845,40 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B365" s="2" t="inlineStr">
+      <c r="A365" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B365" s="3" t="inlineStr">
         <is>
           <t>BA83-06041A</t>
         </is>
       </c>
-      <c r="C365" s="2" t="inlineStr">
+      <c r="C365" s="3" t="inlineStr">
         <is>
           <t>ba83-06041a</t>
         </is>
       </c>
-      <c r="D365" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E365" s="2" t="n"/>
-      <c r="F365" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA83-06041A</t>
-        </is>
-      </c>
-      <c r="G365" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H365" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D365" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E365" s="3" t="n"/>
+      <c r="F365" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Jdm-Gummifuss (Rubber Foot) Titan4-15 - BA83-06041A</t>
+        </is>
+      </c>
+      <c r="G365" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H365" s="3" t="inlineStr">
+        <is>
+          <t>Site title: SAMSUNG BA83-06041A JDM-GUMMIFUSS TITAN4-15 RPL NPC,HQ2581 | JDM-GUMMIFUSS (rubber foot) TITAN4-15 / fits laptop</t>
         </is>
       </c>
     </row>
@@ -15415,40 +15435,40 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B380" s="2" t="inlineStr">
+      <c r="A380" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B380" s="3" t="inlineStr">
         <is>
           <t>BA98-02841A</t>
         </is>
       </c>
-      <c r="C380" s="2" t="inlineStr">
+      <c r="C380" s="3" t="inlineStr">
         <is>
           <t>ba98-02841a</t>
         </is>
       </c>
-      <c r="D380" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E380" s="2" t="n"/>
-      <c r="F380" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA98-02841A</t>
-        </is>
-      </c>
-      <c r="G380" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H380" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D380" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E380" s="3" t="n"/>
+      <c r="F380" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Assembly Hinge-L (Left Hinge Assembly) - BA98-02841A</t>
+        </is>
+      </c>
+      <c r="G380" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H380" s="3" t="inlineStr">
+        <is>
+          <t>Site title: SAMSUNG BA98-02841A ASSY HINGE-L;VENUS-15,SEC,STAINLESS,NATU | Assy Hinge-L (left hinge assembly) / fits laptop</t>
         </is>
       </c>
     </row>
@@ -15967,40 +15987,40 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B394" s="2" t="inlineStr">
+      <c r="A394" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B394" s="3" t="inlineStr">
         <is>
           <t>BA43-00406A</t>
         </is>
       </c>
-      <c r="C394" s="2" t="inlineStr">
+      <c r="C394" s="3" t="inlineStr">
         <is>
           <t>ba43-00406a</t>
         </is>
       </c>
-      <c r="D394" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E394" s="2" t="n"/>
-      <c r="F394" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA43-00406A</t>
-        </is>
-      </c>
-      <c r="G394" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H394" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D394" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E394" s="3" t="n"/>
+      <c r="F394" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Battery - BA43-00406A</t>
+        </is>
+      </c>
+      <c r="G394" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H394" s="3" t="inlineStr">
+        <is>
+          <t>Site title: BA43-00406A original Samsung battery 55,9Wh | Battery / fits laptop</t>
         </is>
       </c>
     </row>
@@ -16279,40 +16299,40 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B402" s="2" t="inlineStr">
+      <c r="A402" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B402" s="3" t="inlineStr">
         <is>
           <t>AH81-15908A</t>
         </is>
       </c>
-      <c r="C402" s="2" t="inlineStr">
+      <c r="C402" s="3" t="inlineStr">
         <is>
           <t>ah81-15908a</t>
         </is>
       </c>
-      <c r="D402" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E402" s="2" t="n"/>
-      <c r="F402" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-15908A</t>
-        </is>
-      </c>
-      <c r="G402" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H402" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D402" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E402" s="3" t="n"/>
+      <c r="F402" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Wheel Assembly Jdm - AH81-15908A</t>
+        </is>
+      </c>
+      <c r="G402" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H402" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ah81 15908a | JDM-Wheel Assembly / fits speaker/soundbar</t>
         </is>
       </c>
     </row>
@@ -17352,7 +17372,7 @@
       <c r="E429" s="3" t="n"/>
       <c r="F429" s="3" t="inlineStr">
         <is>
-          <t>Samsung Soundbar Subwoofer– Samsung Parts Usa - AH81-15459A</t>
+          <t>Samsung Soundbar Subwoofer - AH81-15459A</t>
         </is>
       </c>
       <c r="G429" s="3" t="inlineStr">
@@ -17470,7 +17490,7 @@
       <c r="E432" s="3" t="n"/>
       <c r="F432" s="3" t="inlineStr">
         <is>
-          <t>Samsung Washer– Samsung Parts Usa - 6031-001640</t>
+          <t>Samsung Washer - 6031-001640</t>
         </is>
       </c>
       <c r="G432" s="3" t="inlineStr">
@@ -17599,40 +17619,40 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B436" s="2" t="inlineStr">
+      <c r="A436" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B436" s="3" t="inlineStr">
         <is>
           <t>AH81-13948A</t>
         </is>
       </c>
-      <c r="C436" s="2" t="inlineStr">
+      <c r="C436" s="3" t="inlineStr">
         <is>
           <t>ah81-13948a</t>
         </is>
       </c>
-      <c r="D436" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E436" s="2" t="n"/>
-      <c r="F436" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-13948A</t>
-        </is>
-      </c>
-      <c r="G436" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H436" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D436" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E436" s="3" t="n"/>
+      <c r="F436" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Service Jdm Assembly Pba Bt Module (Bluetooth Module) - AH81-13948A</t>
+        </is>
+      </c>
+      <c r="G436" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H436" s="3" t="inlineStr">
+        <is>
+          <t>Site title: AH81-13948A Svc Jdm Assembly Pba Bt Module | SVC JDM Assembly PBA BT Module (Bluetooth module) / fits speaker/soundbar</t>
         </is>
       </c>
     </row>
@@ -17679,78 +17699,78 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B438" s="2" t="inlineStr">
+      <c r="A438" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B438" s="3" t="inlineStr">
         <is>
           <t>AH81-11552A</t>
         </is>
       </c>
-      <c r="C438" s="2" t="inlineStr">
+      <c r="C438" s="3" t="inlineStr">
         <is>
           <t>ah81-11552a</t>
         </is>
       </c>
-      <c r="D438" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E438" s="2" t="n"/>
-      <c r="F438" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-11552A</t>
-        </is>
-      </c>
-      <c r="G438" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H438" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D438" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E438" s="3" t="n"/>
+      <c r="F438" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Speaker Assembly (1 Unit Spk Assy) - AH81-11552A</t>
+        </is>
+      </c>
+      <c r="G438" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H438" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ah81 11552a | Speaker assembly (A/S-1 UNIT SPK ASSY) / fits speaker/soundbar</t>
         </is>
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B439" s="2" t="inlineStr">
+      <c r="A439" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B439" s="3" t="inlineStr">
         <is>
           <t>BA98-01447A</t>
         </is>
       </c>
-      <c r="C439" s="2" t="inlineStr">
+      <c r="C439" s="3" t="inlineStr">
         <is>
           <t>ba98-01447a</t>
         </is>
       </c>
-      <c r="D439" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E439" s="2" t="n"/>
-      <c r="F439" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA98-01447A</t>
-        </is>
-      </c>
-      <c r="G439" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H439" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D439" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E439" s="3" t="n"/>
+      <c r="F439" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Bottom Case Rear Assembly - BA98-01447A</t>
+        </is>
+      </c>
+      <c r="G439" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H439" s="3" t="inlineStr">
+        <is>
+          <t>Site title: BA98-01447A ASSEMBLY CASE REAR-BOTTOM | Assembly Case Rear-Bottom / fits Chromebook laptop</t>
         </is>
       </c>
     </row>
@@ -18513,78 +18533,78 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B459" s="2" t="inlineStr">
+      <c r="A459" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B459" s="3" t="inlineStr">
         <is>
           <t>BA98-03727A</t>
         </is>
       </c>
-      <c r="C459" s="2" t="inlineStr">
+      <c r="C459" s="3" t="inlineStr">
         <is>
           <t>ba98-03727a</t>
         </is>
       </c>
-      <c r="D459" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E459" s="2" t="n"/>
-      <c r="F459" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA98-03727A</t>
-        </is>
-      </c>
-      <c r="G459" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H459" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D459" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E459" s="3" t="n"/>
+      <c r="F459" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Foot Back Rubber Assembly - BA98-03727A</t>
+        </is>
+      </c>
+      <c r="G459" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H459" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung BA98-03727A Assembly Rubber-Foot_Back;Venu | Assembly Rubber-Foot Back / fits laptop (Galaxy Book3 Pro 14)</t>
         </is>
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B460" s="2" t="inlineStr">
+      <c r="A460" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B460" s="3" t="inlineStr">
         <is>
           <t>AH81-16904A</t>
         </is>
       </c>
-      <c r="C460" s="2" t="inlineStr">
+      <c r="C460" s="3" t="inlineStr">
         <is>
           <t>ah81-16904a</t>
         </is>
       </c>
-      <c r="D460" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E460" s="2" t="n"/>
-      <c r="F460" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-16904A</t>
-        </is>
-      </c>
-      <c r="G460" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H460" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D460" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E460" s="3" t="n"/>
+      <c r="F460" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Service Jdm-Smps (Service Part) - AH81-16904A</t>
+        </is>
+      </c>
+      <c r="G460" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H460" s="3" t="inlineStr">
+        <is>
+          <t>Site title: SAM AH81 16904A | Svc Jdm-Smps (service part) / fits None</t>
         </is>
       </c>
     </row>
@@ -18745,40 +18765,40 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B465" s="2" t="inlineStr">
+      <c r="A465" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B465" s="3" t="inlineStr">
         <is>
           <t>BA39-01473A</t>
         </is>
       </c>
-      <c r="C465" s="2" t="inlineStr">
+      <c r="C465" s="3" t="inlineStr">
         <is>
           <t>ba39-01473a</t>
         </is>
       </c>
-      <c r="D465" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E465" s="2" t="n"/>
-      <c r="F465" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA39-01473A</t>
-        </is>
-      </c>
-      <c r="G465" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H465" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D465" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E465" s="3" t="n"/>
+      <c r="F465" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop LCD Cable Cable Harness - BA39-01473A</t>
+        </is>
+      </c>
+      <c r="G465" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H465" s="3" t="inlineStr">
+        <is>
+          <t>Site title: BA39-01473A CBF HARNESS-LCD CABLE;JOAN-11, | CBF Harness-LCD Cable / fits Chromebook laptop</t>
         </is>
       </c>
     </row>
@@ -19792,7 +19812,7 @@
       <c r="E491" s="3" t="n"/>
       <c r="F491" s="3" t="inlineStr">
         <is>
-          <t>Samsung Refrigerator W Lan Module– Samsung Parts Usa - 4709-002927</t>
+          <t>Samsung Refrigerator W Lan Module - 4709-002927</t>
         </is>
       </c>
       <c r="G491" s="3" t="inlineStr">
@@ -20146,7 +20166,7 @@
       <c r="E500" s="3" t="n"/>
       <c r="F500" s="3" t="inlineStr">
         <is>
-          <t>Samsung TV Crystal-Smd– Samsung Parts Usa - 2801-004284</t>
+          <t>Samsung TV Smd Crystal - 2801-004284</t>
         </is>
       </c>
       <c r="G500" s="3" t="inlineStr">
@@ -22366,7 +22386,7 @@
       <c r="E556" s="3" t="n"/>
       <c r="F556" s="3" t="inlineStr">
         <is>
-          <t>Samsung Main PCB Board Assembly– Samsung Parts Usa - AH94-02511A</t>
+          <t>Samsung Main PCB Board Assembly - AH94-02511A</t>
         </is>
       </c>
       <c r="G556" s="3" t="inlineStr">
@@ -22495,40 +22515,40 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B560" s="2" t="inlineStr">
+      <c r="A560" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B560" s="3" t="inlineStr">
         <is>
           <t>AH94-03721D</t>
         </is>
       </c>
-      <c r="C560" s="2" t="inlineStr">
+      <c r="C560" s="3" t="inlineStr">
         <is>
           <t>ah94-03721d</t>
         </is>
       </c>
-      <c r="D560" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E560" s="2" t="n"/>
-      <c r="F560" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH94-03721D</t>
-        </is>
-      </c>
-      <c r="G560" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H560" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D560" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E560" s="3" t="n"/>
+      <c r="F560" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar PCB Assembly Amp - AH94-03721D</t>
+        </is>
+      </c>
+      <c r="G560" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H560" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ah94 03721d | PCB Assembly Amp / fits speaker/soundbar</t>
         </is>
       </c>
     </row>
@@ -23915,40 +23935,40 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B596" s="2" t="inlineStr">
+      <c r="A596" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B596" s="3" t="inlineStr">
         <is>
           <t>AH81-11584A</t>
         </is>
       </c>
-      <c r="C596" s="2" t="inlineStr">
+      <c r="C596" s="3" t="inlineStr">
         <is>
           <t>ah81-11584a</t>
         </is>
       </c>
-      <c r="D596" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E596" s="2" t="n"/>
-      <c r="F596" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-11584A</t>
-        </is>
-      </c>
-      <c r="G596" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H596" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D596" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E596" s="3" t="n"/>
+      <c r="F596" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Unit Spk (Speaker Unit) - AH81-11584A</t>
+        </is>
+      </c>
+      <c r="G596" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H596" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ah81 11584a | A/S-UNIT SPK (speaker unit) / fits speaker/soundbar</t>
         </is>
       </c>
     </row>
@@ -24288,7 +24308,7 @@
       <c r="E605" s="3" t="n"/>
       <c r="F605" s="3" t="inlineStr">
         <is>
-          <t>Samsung Soundbar Assembly-Smps Power Board– Samsung Parts Usa - AH82-02250A</t>
+          <t>Samsung Soundbar Smps Power Board Assembly - AH82-02250A</t>
         </is>
       </c>
       <c r="G605" s="3" t="inlineStr">
@@ -25677,40 +25697,40 @@
       </c>
     </row>
     <row r="641">
-      <c r="A641" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B641" s="2" t="inlineStr">
+      <c r="A641" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B641" s="3" t="inlineStr">
         <is>
           <t>AH82-02597A</t>
         </is>
       </c>
-      <c r="C641" s="2" t="inlineStr">
+      <c r="C641" s="3" t="inlineStr">
         <is>
           <t>ah82-02597a</t>
         </is>
       </c>
-      <c r="D641" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E641" s="2" t="n"/>
-      <c r="F641" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH82-02597A</t>
-        </is>
-      </c>
-      <c r="G641" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H641" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D641" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E641" s="3" t="n"/>
+      <c r="F641" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Bracket P Wall A Assembly - AH82-02597A</t>
+        </is>
+      </c>
+      <c r="G641" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H641" s="3" t="inlineStr">
+        <is>
+          <t>Site title: samsung ah82 02597a a s assembly bracket p wall a | A/S Assembly Bracket P Wall A / fits None</t>
         </is>
       </c>
     </row>
@@ -25829,40 +25849,40 @@
       </c>
     </row>
     <row r="645">
-      <c r="A645" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B645" s="2" t="inlineStr">
+      <c r="A645" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B645" s="3" t="inlineStr">
         <is>
           <t>BA83-06059A</t>
         </is>
       </c>
-      <c r="C645" s="2" t="inlineStr">
+      <c r="C645" s="3" t="inlineStr">
         <is>
           <t>ba83-06059a</t>
         </is>
       </c>
-      <c r="D645" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E645" s="2" t="n"/>
-      <c r="F645" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA83-06059A</t>
-        </is>
-      </c>
-      <c r="G645" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H645" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D645" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E645" s="3" t="n"/>
+      <c r="F645" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop LCD Assembly - BA83-06059A</t>
+        </is>
+      </c>
+      <c r="G645" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H645" s="3" t="inlineStr">
+        <is>
+          <t>Site title: SAMSUNG BA83-06059A JDM-LCD BAUGRUPPE;TITAN4-15 RPL NPC,HQ3160001 | LCD Assembly / fits laptop</t>
         </is>
       </c>
     </row>
@@ -26495,40 +26515,40 @@
       </c>
     </row>
     <row r="662">
-      <c r="A662" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B662" s="2" t="inlineStr">
+      <c r="A662" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B662" s="3" t="inlineStr">
         <is>
           <t>BA98-02872A</t>
         </is>
       </c>
-      <c r="C662" s="2" t="inlineStr">
+      <c r="C662" s="3" t="inlineStr">
         <is>
           <t>ba98-02872a</t>
         </is>
       </c>
-      <c r="D662" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E662" s="2" t="n"/>
-      <c r="F662" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA98-02872A</t>
-        </is>
-      </c>
-      <c r="G662" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H662" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D662" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E662" s="3" t="n"/>
+      <c r="F662" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Upper Case Assembly - BA98-02872A</t>
+        </is>
+      </c>
+      <c r="G662" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H662" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ba98 02872a | Upper Case Assembly / fits laptop (Chromebook)</t>
         </is>
       </c>
     </row>
@@ -26777,40 +26797,44 @@
       </c>
     </row>
     <row r="669">
-      <c r="A669" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B669" s="2" t="inlineStr">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
         <is>
           <t>BN07-01395B</t>
         </is>
       </c>
-      <c r="C669" s="2" t="inlineStr">
+      <c r="C669" t="inlineStr">
         <is>
           <t>bn07-01395b</t>
         </is>
       </c>
-      <c r="D669" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E669" s="2" t="n"/>
-      <c r="F669" s="2" t="inlineStr">
-        <is>
-          <t>Samsung TV Replacement Part - BN07-01395B</t>
-        </is>
-      </c>
-      <c r="G669" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H669" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Verified (page found)</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>https://samsungparts.com/products/bn07-01395b</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>Samsung TV LCD Panel - BN07-01395B</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>Site title: bn07 01395b | LCD Panel / fits TV</t>
         </is>
       </c>
     </row>
@@ -27047,40 +27071,40 @@
       </c>
     </row>
     <row r="676">
-      <c r="A676" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B676" s="2" t="inlineStr">
+      <c r="A676" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B676" s="3" t="inlineStr">
         <is>
           <t>BA41-02655A</t>
         </is>
       </c>
-      <c r="C676" s="2" t="inlineStr">
+      <c r="C676" s="3" t="inlineStr">
         <is>
           <t>ba41-02655a</t>
         </is>
       </c>
-      <c r="D676" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E676" s="2" t="n"/>
-      <c r="F676" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA41-02655A</t>
-        </is>
-      </c>
-      <c r="G676" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H676" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D676" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E676" s="3" t="n"/>
+      <c r="F676" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Fpc-Btn (Flex Cable) - BA41-02655A</t>
+        </is>
+      </c>
+      <c r="G676" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H676" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ba41 02655a | FPC-BTN (flex cable) / fits laptop (Chromebook)</t>
         </is>
       </c>
     </row>
@@ -28097,40 +28121,40 @@
       </c>
     </row>
     <row r="703">
-      <c r="A703" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B703" s="2" t="inlineStr">
+      <c r="A703" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B703" s="3" t="inlineStr">
         <is>
           <t>BA98-03669A</t>
         </is>
       </c>
-      <c r="C703" s="2" t="inlineStr">
+      <c r="C703" s="3" t="inlineStr">
         <is>
           <t>ba98-03669a</t>
         </is>
       </c>
-      <c r="D703" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E703" s="2" t="n"/>
-      <c r="F703" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA98-03669A</t>
-        </is>
-      </c>
-      <c r="G703" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H703" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D703" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E703" s="3" t="n"/>
+      <c r="F703" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Rubber Foot Assembly (Front/Rear) - BA98-03669A</t>
+        </is>
+      </c>
+      <c r="G703" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H703" s="3" t="inlineStr">
+        <is>
+          <t>Site title: SAMSUNG BA98-03669A ASSY GUMMIFUSS VORNE HINTEN MARS3-16 WIF | Rubber foot assembly (front/rear) / fits laptop</t>
         </is>
       </c>
     </row>
@@ -28215,40 +28239,40 @@
       </c>
     </row>
     <row r="706">
-      <c r="A706" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B706" s="2" t="inlineStr">
+      <c r="A706" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B706" s="3" t="inlineStr">
         <is>
           <t>AA59-00213A</t>
         </is>
       </c>
-      <c r="C706" s="2" t="inlineStr">
+      <c r="C706" s="3" t="inlineStr">
         <is>
           <t>aa59-00213a</t>
         </is>
       </c>
-      <c r="D706" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E706" s="2" t="n"/>
-      <c r="F706" s="2" t="inlineStr">
-        <is>
-          <t>Samsung AV Replacement Part - AA59-00213A</t>
-        </is>
-      </c>
-      <c r="G706" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H706" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D706" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E706" s="3" t="n"/>
+      <c r="F706" s="3" t="inlineStr">
+        <is>
+          <t>Samsung TV Remote Control - AA59-00213A</t>
+        </is>
+      </c>
+      <c r="G706" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H706" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung AA59-00213A Remote Control - Samsung Parts USA | Remote Control / fits TV</t>
         </is>
       </c>
     </row>
@@ -28935,40 +28959,40 @@
       </c>
     </row>
     <row r="724">
-      <c r="A724" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B724" s="2" t="inlineStr">
+      <c r="A724" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B724" s="3" t="inlineStr">
         <is>
           <t>AH94-03071A</t>
         </is>
       </c>
-      <c r="C724" s="2" t="inlineStr">
+      <c r="C724" s="3" t="inlineStr">
         <is>
           <t>ah94-03071a</t>
         </is>
       </c>
-      <c r="D724" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E724" s="2" t="n"/>
-      <c r="F724" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH94-03071A</t>
-        </is>
-      </c>
-      <c r="G724" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H724" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit (only a sitemap xml listing the URL; no titled product link)</t>
+      <c r="D724" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E724" s="3" t="n"/>
+      <c r="F724" s="3" t="inlineStr">
+        <is>
+          <t>Samsung PCB Assembly Remote Control Ir - AH94-03071A</t>
+        </is>
+      </c>
+      <c r="G724" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H724" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Genuine Samsung PartAH94-03071A - Samsung Home Stereo And Theater PCB Assembly Remote Control IR$40.99 | PCB Assembly Remote Control IR / fits home stereo/theater</t>
         </is>
       </c>
     </row>
@@ -29791,40 +29815,44 @@
       </c>
     </row>
     <row r="746">
-      <c r="A746" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B746" s="2" t="inlineStr">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
         <is>
           <t>AH81-11534A</t>
         </is>
       </c>
-      <c r="C746" s="2" t="inlineStr">
+      <c r="C746" t="inlineStr">
         <is>
           <t>ah81-11534a</t>
         </is>
       </c>
-      <c r="D746" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E746" s="2" t="n"/>
-      <c r="F746" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-11534A</t>
-        </is>
-      </c>
-      <c r="G746" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H746" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Verified (page found)</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>https://samsungparts.com/products/ah81-11534a</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>Samsung TV Main Board Assembly - AH81-11534A</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>Site title: ah81 11534a | A/S Main Board Assembly / fits TV</t>
         </is>
       </c>
     </row>
@@ -31793,40 +31821,44 @@
       </c>
     </row>
     <row r="797">
-      <c r="A797" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B797" s="2" t="inlineStr">
+      <c r="A797" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B797" s="3" t="inlineStr">
         <is>
           <t>AH81-09822A</t>
         </is>
       </c>
-      <c r="C797" s="2" t="inlineStr">
+      <c r="C797" s="3" t="inlineStr">
         <is>
           <t>ah81-09822a</t>
         </is>
       </c>
-      <c r="D797" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E797" s="2" t="n"/>
-      <c r="F797" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-09822A</t>
-        </is>
-      </c>
-      <c r="G797" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H797" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D797" s="3" t="inlineStr">
+        <is>
+          <t>Verified (page found)</t>
+        </is>
+      </c>
+      <c r="E797" s="3" t="inlineStr">
+        <is>
+          <t>https://samsungparts.com/products/ah81-09822a</t>
+        </is>
+      </c>
+      <c r="F797" s="3" t="inlineStr">
+        <is>
+          <t>Samsung TV Etc Sheet - AH81-09822A</t>
+        </is>
+      </c>
+      <c r="G797" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H797" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ah81 09822a | A/S Sheet-Etc / fits sound bar / TV (summary inconsistent)</t>
         </is>
       </c>
     </row>
@@ -33407,40 +33439,40 @@
       </c>
     </row>
     <row r="838">
-      <c r="A838" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B838" s="2" t="inlineStr">
+      <c r="A838" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B838" s="3" t="inlineStr">
         <is>
           <t>BA67-01677A</t>
         </is>
       </c>
-      <c r="C838" s="2" t="inlineStr">
+      <c r="C838" s="3" t="inlineStr">
         <is>
           <t>ba67-01677a</t>
         </is>
       </c>
-      <c r="D838" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E838" s="2" t="n"/>
-      <c r="F838" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA67-01677A</t>
-        </is>
-      </c>
-      <c r="G838" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H838" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D838" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E838" s="3" t="n"/>
+      <c r="F838" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Rubber Foot Bottom (Gummi-Unten, Tpu) - BA67-01677A</t>
+        </is>
+      </c>
+      <c r="G838" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H838" s="3" t="inlineStr">
+        <is>
+          <t>Site title: SAMSUNG BA67-01677A GUMMI-UNTEN_TPU;NX-16,TPU,SCHWARZ | Rubber foot bottom (Gummi-Unten, TPU) / fits laptop (Galaxy Book4 Edge 14 NP940XMA/NP944XMA)</t>
         </is>
       </c>
     </row>
@@ -33563,40 +33595,40 @@
       </c>
     </row>
     <row r="842">
-      <c r="A842" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B842" s="2" t="inlineStr">
+      <c r="A842" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B842" s="3" t="inlineStr">
         <is>
           <t>3405-001032</t>
         </is>
       </c>
-      <c r="C842" s="2" t="inlineStr">
+      <c r="C842" s="3" t="inlineStr">
         <is>
           <t>3405-001032</t>
         </is>
       </c>
-      <c r="D842" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E842" s="2" t="n"/>
-      <c r="F842" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 3405-001032</t>
-        </is>
-      </c>
-      <c r="G842" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H842" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D842" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E842" s="3" t="n"/>
+      <c r="F842" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Microwave Microswitch (Switch-Micro) - 3405-001032</t>
+        </is>
+      </c>
+      <c r="G842" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H842" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung 3405-001032 Microswitch | Microswitch (Switch-Micro) / fits microwave</t>
         </is>
       </c>
     </row>
@@ -33909,40 +33941,40 @@
       </c>
     </row>
     <row r="851">
-      <c r="A851" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B851" s="2" t="inlineStr">
+      <c r="A851" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B851" s="3" t="inlineStr">
         <is>
           <t>AH81-09805A</t>
         </is>
       </c>
-      <c r="C851" s="2" t="inlineStr">
+      <c r="C851" s="3" t="inlineStr">
         <is>
           <t>ah81-09805a</t>
         </is>
       </c>
-      <c r="D851" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E851" s="2" t="n"/>
-      <c r="F851" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-09805A</t>
-        </is>
-      </c>
-      <c r="G851" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H851" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D851" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E851" s="3" t="n"/>
+      <c r="F851" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Assembly PCB Key-Hw-R450 Key P - AH81-09805A</t>
+        </is>
+      </c>
+      <c r="G851" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H851" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ah81 09805a | A/S-Assy Pcb Key-Hw-R450 Key P / fits speaker/soundbar</t>
         </is>
       </c>
     </row>
@@ -34225,40 +34257,44 @@
       </c>
     </row>
     <row r="859">
-      <c r="A859" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B859" s="2" t="inlineStr">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
         <is>
           <t>AH44-00291A</t>
         </is>
       </c>
-      <c r="C859" s="2" t="inlineStr">
+      <c r="C859" t="inlineStr">
         <is>
           <t>ah44-00291a</t>
         </is>
       </c>
-      <c r="D859" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E859" s="2" t="n"/>
-      <c r="F859" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH44-00291A</t>
-        </is>
-      </c>
-      <c r="G859" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H859" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>Verified (page found)</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>https://samsungparts.com/products/ah44-00291a</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>Samsung TV DC Vss Power Supply Board - AH44-00291A</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>Site title: ah44 00291a | DC VSS power supply board / fits TV</t>
         </is>
       </c>
     </row>
@@ -34583,116 +34619,116 @@
       </c>
     </row>
     <row r="868">
-      <c r="A868" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B868" s="2" t="inlineStr">
+      <c r="A868" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B868" s="3" t="inlineStr">
         <is>
           <t>BA43-00386A</t>
         </is>
       </c>
-      <c r="C868" s="2" t="inlineStr">
+      <c r="C868" s="3" t="inlineStr">
         <is>
           <t>ba43-00386a</t>
         </is>
       </c>
-      <c r="D868" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E868" s="2" t="n"/>
-      <c r="F868" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA43-00386A</t>
-        </is>
-      </c>
-      <c r="G868" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H868" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D868" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E868" s="3" t="n"/>
+      <c r="F868" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Incell Battery Pack-P41Gcj-01 - BA43-00386A</t>
+        </is>
+      </c>
+      <c r="G868" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H868" s="3" t="inlineStr">
+        <is>
+          <t>Site title: BA43-00386A Incell Battery Pack-P41Gcj-01- | Incell Battery Pack-P41Gcj-01- / fits laptop</t>
         </is>
       </c>
     </row>
     <row r="869">
-      <c r="A869" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B869" s="2" t="inlineStr">
+      <c r="A869" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B869" s="3" t="inlineStr">
         <is>
           <t>AH81-14142A</t>
         </is>
       </c>
-      <c r="C869" s="2" t="inlineStr">
+      <c r="C869" s="3" t="inlineStr">
         <is>
           <t>ah81-14142a</t>
         </is>
       </c>
-      <c r="D869" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E869" s="2" t="n"/>
-      <c r="F869" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-14142A</t>
-        </is>
-      </c>
-      <c r="G869" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H869" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D869" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E869" s="3" t="n"/>
+      <c r="F869" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Service Jdm Ks1 1 Speaker Rear R - AH81-14142A</t>
+        </is>
+      </c>
+      <c r="G869" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H869" s="3" t="inlineStr">
+        <is>
+          <t>Site title: AH81-14142A Svc Jdm Ks1 1 Speaker Rear R | Svc Jdm Ks1 1 Speaker Rear R / fits speaker/soundbar</t>
         </is>
       </c>
     </row>
     <row r="870">
-      <c r="A870" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B870" s="2" t="inlineStr">
+      <c r="A870" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B870" s="3" t="inlineStr">
         <is>
           <t>3711-007975</t>
         </is>
       </c>
-      <c r="C870" s="2" t="inlineStr">
+      <c r="C870" s="3" t="inlineStr">
         <is>
           <t>3711-007975</t>
         </is>
       </c>
-      <c r="D870" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E870" s="2" t="n"/>
-      <c r="F870" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 3711-007975</t>
-        </is>
-      </c>
-      <c r="G870" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H870" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D870" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E870" s="3" t="n"/>
+      <c r="F870" s="3" t="inlineStr">
+        <is>
+          <t>Samsung TV Header Connector - 3711-007975</t>
+        </is>
+      </c>
+      <c r="G870" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H870" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 3711-007975 CONNECTOR-HEADER | Connector-Header / fits TV</t>
         </is>
       </c>
     </row>
@@ -35341,40 +35377,40 @@
       </c>
     </row>
     <row r="887">
-      <c r="A887" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B887" s="2" t="inlineStr">
+      <c r="A887" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B887" s="3" t="inlineStr">
         <is>
           <t>AH07-00288F</t>
         </is>
       </c>
-      <c r="C887" s="2" t="inlineStr">
+      <c r="C887" s="3" t="inlineStr">
         <is>
           <t>ah07-00288f</t>
         </is>
       </c>
-      <c r="D887" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E887" s="2" t="n"/>
-      <c r="F887" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH07-00288F</t>
-        </is>
-      </c>
-      <c r="G887" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H887" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D887" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E887" s="3" t="n"/>
+      <c r="F887" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar OLED Display Pm - AH07-00288F</t>
+        </is>
+      </c>
+      <c r="G887" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H887" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ah07 00288f samsung oled display pm | OLED Display PM / fits soundbar</t>
         </is>
       </c>
     </row>
@@ -35501,40 +35537,40 @@
       </c>
     </row>
     <row r="891">
-      <c r="A891" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B891" s="2" t="inlineStr">
+      <c r="A891" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B891" s="3" t="inlineStr">
         <is>
           <t>AH81-15581A</t>
         </is>
       </c>
-      <c r="C891" s="2" t="inlineStr">
+      <c r="C891" s="3" t="inlineStr">
         <is>
           <t>ah81-15581a</t>
         </is>
       </c>
-      <c r="D891" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E891" s="2" t="n"/>
-      <c r="F891" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-15581A</t>
-        </is>
-      </c>
-      <c r="G891" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H891" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D891" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E891" s="3" t="n"/>
+      <c r="F891" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Remote Control - AH81-15581A</t>
+        </is>
+      </c>
+      <c r="G891" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H891" s="3" t="inlineStr">
+        <is>
+          <t>Site title: samsung AH81-15581A REMOTE CONTROL | Remote Control / fits speaker/soundbar</t>
         </is>
       </c>
     </row>
@@ -36003,78 +36039,78 @@
       </c>
     </row>
     <row r="904">
-      <c r="A904" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B904" s="2" t="inlineStr">
+      <c r="A904" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B904" s="3" t="inlineStr">
         <is>
           <t>AH81-11501A</t>
         </is>
       </c>
-      <c r="C904" s="2" t="inlineStr">
+      <c r="C904" s="3" t="inlineStr">
         <is>
           <t>ah81-11501a</t>
         </is>
       </c>
-      <c r="D904" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E904" s="2" t="n"/>
-      <c r="F904" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-11501A</t>
-        </is>
-      </c>
-      <c r="G904" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H904" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D904" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E904" s="3" t="n"/>
+      <c r="F904" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar DC Fan - AH81-11501A</t>
+        </is>
+      </c>
+      <c r="G904" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H904" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ah81 11501a | A/S-DC Fan / fits speaker/soundbar</t>
         </is>
       </c>
     </row>
     <row r="905">
-      <c r="A905" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B905" s="2" t="inlineStr">
+      <c r="A905" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B905" s="3" t="inlineStr">
         <is>
           <t>99002608</t>
         </is>
       </c>
-      <c r="C905" s="2" t="inlineStr">
+      <c r="C905" s="3" t="inlineStr">
         <is>
           <t>99002608</t>
         </is>
       </c>
-      <c r="D905" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E905" s="2" t="n"/>
-      <c r="F905" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 99002608</t>
-        </is>
-      </c>
-      <c r="G905" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H905" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D905" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E905" s="3" t="n"/>
+      <c r="F905" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Dishwasher Cable Bracket Roller - 99002608</t>
+        </is>
+      </c>
+      <c r="G905" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H905" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung 99002608 Dishwasher Cable Bracket Roller - Samsung Parts USA | Dishwasher Cable Bracket Roller / fits dishwasher</t>
         </is>
       </c>
     </row>
@@ -36117,40 +36153,40 @@
       </c>
     </row>
     <row r="907">
-      <c r="A907" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B907" s="2" t="inlineStr">
+      <c r="A907" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B907" s="3" t="inlineStr">
         <is>
           <t>AH94-00021P</t>
         </is>
       </c>
-      <c r="C907" s="2" t="inlineStr">
+      <c r="C907" s="3" t="inlineStr">
         <is>
           <t>ah94-00021p</t>
         </is>
       </c>
-      <c r="D907" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E907" s="2" t="n"/>
-      <c r="F907" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH94-00021P</t>
-        </is>
-      </c>
-      <c r="G907" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H907" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D907" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E907" s="3" t="n"/>
+      <c r="F907" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Power Control Board K Assembly - AH94-00021P</t>
+        </is>
+      </c>
+      <c r="G907" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H907" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ah94 00021p | Assembly Power Control Board K / fits speaker/soundbar</t>
         </is>
       </c>
     </row>
@@ -36555,40 +36591,40 @@
       </c>
     </row>
     <row r="918">
-      <c r="A918" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B918" s="2" t="inlineStr">
+      <c r="A918" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B918" s="3" t="inlineStr">
         <is>
           <t>AH81-09828A</t>
         </is>
       </c>
-      <c r="C918" s="2" t="inlineStr">
+      <c r="C918" s="3" t="inlineStr">
         <is>
           <t>ah81-09828a</t>
         </is>
       </c>
-      <c r="D918" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E918" s="2" t="n"/>
-      <c r="F918" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-09828A</t>
-        </is>
-      </c>
-      <c r="G918" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H918" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D918" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E918" s="3" t="n"/>
+      <c r="F918" s="3" t="inlineStr">
+        <is>
+          <t>Samsung TV Screw-Taptype Nscbh00016A - AH81-09828A</t>
+        </is>
+      </c>
+      <c r="G918" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H918" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung AH81-09828A A/S-Screw-Taptype Nscbh00016A | A/S-Screw-Taptype Nscbh00016A / fits TV</t>
         </is>
       </c>
     </row>
@@ -39843,40 +39879,44 @@
       </c>
     </row>
     <row r="1002">
-      <c r="A1002" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1002" s="2" t="inlineStr">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
         <is>
           <t>BA44-00346A</t>
         </is>
       </c>
-      <c r="C1002" s="2" t="inlineStr">
+      <c r="C1002" t="inlineStr">
         <is>
           <t>ba44-00346a</t>
         </is>
       </c>
-      <c r="D1002" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1002" s="2" t="n"/>
-      <c r="F1002" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA44-00346A</t>
-        </is>
-      </c>
-      <c r="G1002" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1002" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>Verified (page found)</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>https://samsungparts.com/products/ba44-00346a</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Adaptor (Ac Adapter) - BA44-00346A</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>Site title: ba44 00346a | Adaptor (AC adapter) / fits laptop</t>
         </is>
       </c>
     </row>
@@ -40513,40 +40553,40 @@
       </c>
     </row>
     <row r="1019">
-      <c r="A1019" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1019" s="2" t="inlineStr">
+      <c r="A1019" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1019" s="3" t="inlineStr">
         <is>
           <t>BA42-00668A</t>
         </is>
       </c>
-      <c r="C1019" s="2" t="inlineStr">
+      <c r="C1019" s="3" t="inlineStr">
         <is>
           <t>ba42-00668a</t>
         </is>
       </c>
-      <c r="D1019" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1019" s="2" t="n"/>
-      <c r="F1019" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA42-00668A</t>
-        </is>
-      </c>
-      <c r="G1019" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1019" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1019" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1019" s="3" t="n"/>
+      <c r="F1019" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Main Antenna - BA42-00668A</t>
+        </is>
+      </c>
+      <c r="G1019" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1019" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ba42 00668a | Antenna-Main / fits None</t>
         </is>
       </c>
     </row>
@@ -42655,40 +42695,44 @@
       </c>
     </row>
     <row r="1074">
-      <c r="A1074" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1074" s="2" t="inlineStr">
+      <c r="A1074" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1074" s="3" t="inlineStr">
         <is>
           <t>AH82-02232A</t>
         </is>
       </c>
-      <c r="C1074" s="2" t="inlineStr">
+      <c r="C1074" s="3" t="inlineStr">
         <is>
           <t>ah82-02232a</t>
         </is>
       </c>
-      <c r="D1074" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1074" s="2" t="n"/>
-      <c r="F1074" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH82-02232A</t>
-        </is>
-      </c>
-      <c r="G1074" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1074" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1074" s="3" t="inlineStr">
+        <is>
+          <t>Verified (page found)</t>
+        </is>
+      </c>
+      <c r="E1074" s="3" t="inlineStr">
+        <is>
+          <t>https://samsungparts.com/products/ah82-02232a</t>
+        </is>
+      </c>
+      <c r="F1074" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Rear Speaker P - AH82-02232A</t>
+        </is>
+      </c>
+      <c r="G1074" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1074" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ah82 02232a | Speaker P-Rear / fits home theater / TV</t>
         </is>
       </c>
     </row>
@@ -42895,78 +42939,78 @@
       </c>
     </row>
     <row r="1080">
-      <c r="A1080" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1080" s="2" t="inlineStr">
+      <c r="A1080" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1080" s="3" t="inlineStr">
         <is>
           <t>BA41-02458A</t>
         </is>
       </c>
-      <c r="C1080" s="2" t="inlineStr">
+      <c r="C1080" s="3" t="inlineStr">
         <is>
           <t>ba41-02458a</t>
         </is>
       </c>
-      <c r="D1080" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1080" s="2" t="n"/>
-      <c r="F1080" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA41-02458A</t>
-        </is>
-      </c>
-      <c r="G1080" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1080" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1080" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1080" s="3" t="n"/>
+      <c r="F1080" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Touchpad FFC - BA41-02458A</t>
+        </is>
+      </c>
+      <c r="G1080" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1080" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ba41 02458a | FFC-Touchpad / fits laptop</t>
         </is>
       </c>
     </row>
     <row r="1081">
-      <c r="A1081" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1081" s="2" t="inlineStr">
+      <c r="A1081" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1081" s="3" t="inlineStr">
         <is>
           <t>BA42-00681A</t>
         </is>
       </c>
-      <c r="C1081" s="2" t="inlineStr">
+      <c r="C1081" s="3" t="inlineStr">
         <is>
           <t>ba42-00681a</t>
         </is>
       </c>
-      <c r="D1081" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1081" s="2" t="n"/>
-      <c r="F1081" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA42-00681A</t>
-        </is>
-      </c>
-      <c r="G1081" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1081" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1081" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1081" s="3" t="n"/>
+      <c r="F1081" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Antenna Main - BA42-00681A</t>
+        </is>
+      </c>
+      <c r="G1081" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1081" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ba42 00681a | Antenna Main / fits None</t>
         </is>
       </c>
     </row>
@@ -43169,40 +43213,44 @@
       </c>
     </row>
     <row r="1087">
-      <c r="A1087" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1087" s="2" t="inlineStr">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
         <is>
           <t>AH94-03634B</t>
         </is>
       </c>
-      <c r="C1087" s="2" t="inlineStr">
+      <c r="C1087" t="inlineStr">
         <is>
           <t>ah94-03634b</t>
         </is>
       </c>
-      <c r="D1087" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1087" s="2" t="n"/>
-      <c r="F1087" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH94-03634B</t>
-        </is>
-      </c>
-      <c r="G1087" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1087" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>Verified (page found)</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>https://samsungparts.com/products/ah94-03634b</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Front PCB Assembly - AH94-03634B</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>Site title: ah94 03634b | Front PCB Assembly / fits home theater</t>
         </is>
       </c>
     </row>
@@ -44147,40 +44195,40 @@
       </c>
     </row>
     <row r="1112">
-      <c r="A1112" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1112" s="2" t="inlineStr">
+      <c r="A1112" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1112" s="3" t="inlineStr">
         <is>
           <t>BA61-04885A</t>
         </is>
       </c>
-      <c r="C1112" s="2" t="inlineStr">
+      <c r="C1112" s="3" t="inlineStr">
         <is>
           <t>ba61-04885a</t>
         </is>
       </c>
-      <c r="D1112" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1112" s="2" t="n"/>
-      <c r="F1112" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA61-04885A</t>
-        </is>
-      </c>
-      <c r="G1112" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1112" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1112" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1112" s="3" t="n"/>
+      <c r="F1112" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Touchpad Contact - BA61-04885A</t>
+        </is>
+      </c>
+      <c r="G1112" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1112" s="3" t="inlineStr">
+        <is>
+          <t>Site title: samsung BA61-04885A CONTACT-TOUCHPAD | Contact-Touchpad / fits Chromebook</t>
         </is>
       </c>
     </row>
@@ -44665,40 +44713,40 @@
       </c>
     </row>
     <row r="1125">
-      <c r="A1125" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1125" s="2" t="inlineStr">
+      <c r="A1125" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1125" s="3" t="inlineStr">
         <is>
           <t>AH81-13768A</t>
         </is>
       </c>
-      <c r="C1125" s="2" t="inlineStr">
+      <c r="C1125" s="3" t="inlineStr">
         <is>
           <t>ah81-13768a</t>
         </is>
       </c>
-      <c r="D1125" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1125" s="2" t="n"/>
-      <c r="F1125" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-13768A</t>
-        </is>
-      </c>
-      <c r="G1125" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1125" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1125" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1125" s="3" t="n"/>
+      <c r="F1125" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Service Jdm-Network-Wireless Audio - AH81-13768A</t>
+        </is>
+      </c>
+      <c r="G1125" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1125" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ah81 13768a | Svc Jdm-Network-Wireless Audio / fits speaker/soundbar</t>
         </is>
       </c>
     </row>
@@ -44859,40 +44907,40 @@
       </c>
     </row>
     <row r="1130">
-      <c r="A1130" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1130" s="2" t="inlineStr">
+      <c r="A1130" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1130" s="3" t="inlineStr">
         <is>
           <t>AH81-15338A</t>
         </is>
       </c>
-      <c r="C1130" s="2" t="inlineStr">
+      <c r="C1130" s="3" t="inlineStr">
         <is>
           <t>ah81-15338a</t>
         </is>
       </c>
-      <c r="D1130" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1130" s="2" t="n"/>
-      <c r="F1130" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-15338A</t>
-        </is>
-      </c>
-      <c r="G1130" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1130" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1130" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1130" s="3" t="n"/>
+      <c r="F1130" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Assembly OLED Service Jdm - AH81-15338A</t>
+        </is>
+      </c>
+      <c r="G1130" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1130" s="3" t="inlineStr">
+        <is>
+          <t>Site title: samsung AH81-15338A SERVICE JDM-ASSEMBLY OLED | Service JDM-Assembly OLED / fits speaker/soundbar</t>
         </is>
       </c>
     </row>
@@ -45929,40 +45977,40 @@
       </c>
     </row>
     <row r="1157">
-      <c r="A1157" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1157" s="2" t="inlineStr">
+      <c r="A1157" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1157" s="3" t="inlineStr">
         <is>
           <t>AH81-15502A</t>
         </is>
       </c>
-      <c r="C1157" s="2" t="inlineStr">
+      <c r="C1157" s="3" t="inlineStr">
         <is>
           <t>ah81-15502a</t>
         </is>
       </c>
-      <c r="D1157" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1157" s="2" t="n"/>
-      <c r="F1157" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-15502A</t>
-        </is>
-      </c>
-      <c r="G1157" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1157" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1157" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1157" s="3" t="n"/>
+      <c r="F1157" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Power Cord Service Jdm - AH81-15502A</t>
+        </is>
+      </c>
+      <c r="G1157" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1157" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ah81 15502a | Service JDM-Power Cord / fits speaker/soundbar</t>
         </is>
       </c>
     </row>
@@ -47513,40 +47561,40 @@
       </c>
     </row>
     <row r="1197">
-      <c r="A1197" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1197" s="2" t="inlineStr">
+      <c r="A1197" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1197" s="3" t="inlineStr">
         <is>
           <t>6044-001172</t>
         </is>
       </c>
-      <c r="C1197" s="2" t="inlineStr">
+      <c r="C1197" s="3" t="inlineStr">
         <is>
           <t>6044-001172</t>
         </is>
       </c>
-      <c r="D1197" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1197" s="2" t="n"/>
-      <c r="F1197" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 6044-001172</t>
-        </is>
-      </c>
-      <c r="G1197" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1197" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1197" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1197" s="3" t="n"/>
+      <c r="F1197" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Og Ring - 6044-001172</t>
+        </is>
+      </c>
+      <c r="G1197" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1197" s="3" t="inlineStr">
+        <is>
+          <t>Site title: SAM 6044 001172 | Ring-Og / fits None</t>
         </is>
       </c>
     </row>
@@ -47981,40 +48029,40 @@
       </c>
     </row>
     <row r="1209">
-      <c r="A1209" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1209" s="2" t="inlineStr">
+      <c r="A1209" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1209" s="3" t="inlineStr">
         <is>
           <t>6009-001548</t>
         </is>
       </c>
-      <c r="C1209" s="2" t="inlineStr">
+      <c r="C1209" s="3" t="inlineStr">
         <is>
           <t>6009-001548</t>
         </is>
       </c>
-      <c r="D1209" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1209" s="2" t="n"/>
-      <c r="F1209" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 6009-001548</t>
-        </is>
-      </c>
-      <c r="G1209" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1209" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1209" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1209" s="3" t="n"/>
+      <c r="F1209" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Refrigerator Screw - 6009-001548</t>
+        </is>
+      </c>
+      <c r="G1209" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1209" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung 6009-001548 Refrigerator Screw | Screw / fits refrigerator</t>
         </is>
       </c>
     </row>
@@ -48179,40 +48227,40 @@
       </c>
     </row>
     <row r="1214">
-      <c r="A1214" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1214" s="2" t="inlineStr">
+      <c r="A1214" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1214" s="3" t="inlineStr">
         <is>
           <t>BN07-01736A</t>
         </is>
       </c>
-      <c r="C1214" s="2" t="inlineStr">
+      <c r="C1214" s="3" t="inlineStr">
         <is>
           <t>bn07-01736a</t>
         </is>
       </c>
-      <c r="D1214" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1214" s="2" t="n"/>
-      <c r="F1214" s="2" t="inlineStr">
-        <is>
-          <t>Samsung TV Replacement Part - BN07-01736A</t>
-        </is>
-      </c>
-      <c r="G1214" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1214" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1214" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1214" s="3" t="n"/>
+      <c r="F1214" s="3" t="inlineStr">
+        <is>
+          <t>Samsung TV LED Display Module - BN07-01736A</t>
+        </is>
+      </c>
+      <c r="G1214" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1214" s="3" t="inlineStr">
+        <is>
+          <t>Site title: bn07 01736a samsung 43 inch class tu7000b 4k uhd hdr smart tv led display module | LED Display Module / fits TV</t>
         </is>
       </c>
     </row>
@@ -49093,40 +49141,40 @@
       </c>
     </row>
     <row r="1237">
-      <c r="A1237" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1237" s="2" t="inlineStr">
+      <c r="A1237" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1237" s="3" t="inlineStr">
         <is>
           <t>6021-001588</t>
         </is>
       </c>
-      <c r="C1237" s="2" t="inlineStr">
+      <c r="C1237" s="3" t="inlineStr">
         <is>
           <t>6021-001588</t>
         </is>
       </c>
-      <c r="D1237" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1237" s="2" t="n"/>
-      <c r="F1237" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 6021-001588</t>
-        </is>
-      </c>
-      <c r="G1237" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1237" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1237" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1237" s="3" t="n"/>
+      <c r="F1237" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Nut Washer - 6021-001588</t>
+        </is>
+      </c>
+      <c r="G1237" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1237" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 6021-001588 Nut Washer | Nut Washer / fits washer</t>
         </is>
       </c>
     </row>
@@ -49207,40 +49255,40 @@
       </c>
     </row>
     <row r="1240">
-      <c r="A1240" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1240" s="2" t="inlineStr">
+      <c r="A1240" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1240" s="3" t="inlineStr">
         <is>
           <t>AH85-01104A</t>
         </is>
       </c>
-      <c r="C1240" s="2" t="inlineStr">
+      <c r="C1240" s="3" t="inlineStr">
         <is>
           <t>ah85-01104a</t>
         </is>
       </c>
-      <c r="D1240" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1240" s="2" t="n"/>
-      <c r="F1240" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH85-01104A</t>
-        </is>
-      </c>
-      <c r="G1240" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1240" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1240" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1240" s="3" t="n"/>
+      <c r="F1240" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Na-Bracket P-Wall Assembly - AH85-01104A</t>
+        </is>
+      </c>
+      <c r="G1240" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1240" s="3" t="inlineStr">
+        <is>
+          <t>Site title: samsung ah85 01104a oem assembly na bracket p wall | Assembly Na-Bracket P-Wall / fits None</t>
         </is>
       </c>
     </row>
@@ -49439,40 +49487,40 @@
       </c>
     </row>
     <row r="1246">
-      <c r="A1246" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1246" s="2" t="inlineStr">
+      <c r="A1246" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1246" s="3" t="inlineStr">
         <is>
           <t>AD44-00161A</t>
         </is>
       </c>
-      <c r="C1246" s="2" t="inlineStr">
+      <c r="C1246" s="3" t="inlineStr">
         <is>
           <t>ad44-00161a</t>
         </is>
       </c>
-      <c r="D1246" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1246" s="2" t="n"/>
-      <c r="F1246" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - AD44-00161A</t>
-        </is>
-      </c>
-      <c r="G1246" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1246" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1246" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1246" s="3" t="n"/>
+      <c r="F1246" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Adaptor - AD44-00161A</t>
+        </is>
+      </c>
+      <c r="G1246" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1246" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ad44 00161a | Adaptor / fits None</t>
         </is>
       </c>
     </row>
@@ -49747,40 +49795,40 @@
       </c>
     </row>
     <row r="1254">
-      <c r="A1254" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1254" s="2" t="inlineStr">
+      <c r="A1254" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1254" s="3" t="inlineStr">
         <is>
           <t>AH81-13957A</t>
         </is>
       </c>
-      <c r="C1254" s="2" t="inlineStr">
+      <c r="C1254" s="3" t="inlineStr">
         <is>
           <t>ah81-13957a</t>
         </is>
       </c>
-      <c r="D1254" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1254" s="2" t="n"/>
-      <c r="F1254" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-13957A</t>
-        </is>
-      </c>
-      <c r="G1254" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1254" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1254" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1254" s="3" t="n"/>
+      <c r="F1254" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Service Jdm Speaker Woofer - AH81-13957A</t>
+        </is>
+      </c>
+      <c r="G1254" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1254" s="3" t="inlineStr">
+        <is>
+          <t>Site title: SAM AH81 13957A | Svc Jdm Speaker Woofer / fits None</t>
         </is>
       </c>
     </row>
@@ -49823,40 +49871,40 @@
       </c>
     </row>
     <row r="1256">
-      <c r="A1256" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1256" s="2" t="inlineStr">
+      <c r="A1256" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1256" s="3" t="inlineStr">
         <is>
           <t>6009-001777</t>
         </is>
       </c>
-      <c r="C1256" s="2" t="inlineStr">
+      <c r="C1256" s="3" t="inlineStr">
         <is>
           <t>6009-001777</t>
         </is>
       </c>
-      <c r="D1256" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1256" s="2" t="n"/>
-      <c r="F1256" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 6009-001777</t>
-        </is>
-      </c>
-      <c r="G1256" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1256" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1256" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1256" s="3" t="n"/>
+      <c r="F1256" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Washer Screw - 6009-001777</t>
+        </is>
+      </c>
+      <c r="G1256" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1256" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 6009-001777 Dishwasher Screw | Screw / fits dishwasher</t>
         </is>
       </c>
     </row>
@@ -51487,40 +51535,40 @@
       </c>
     </row>
     <row r="1298">
-      <c r="A1298" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1298" s="2" t="inlineStr">
+      <c r="A1298" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1298" s="3" t="inlineStr">
         <is>
           <t>AH81-15058A</t>
         </is>
       </c>
-      <c r="C1298" s="2" t="inlineStr">
+      <c r="C1298" s="3" t="inlineStr">
         <is>
           <t>ah81-15058a</t>
         </is>
       </c>
-      <c r="D1298" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1298" s="2" t="n"/>
-      <c r="F1298" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-15058A</t>
-        </is>
-      </c>
-      <c r="G1298" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1298" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit (only AH81-15058C)</t>
+      <c r="D1298" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1298" s="3" t="n"/>
+      <c r="F1298" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Adaptor - AH81-15058A</t>
+        </is>
+      </c>
+      <c r="G1298" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1298" s="3" t="inlineStr">
+        <is>
+          <t>Site title: samsung AH81-15058A ADAPTOR | Adaptor / fits None</t>
         </is>
       </c>
     </row>
@@ -52317,40 +52365,40 @@
       </c>
     </row>
     <row r="1319">
-      <c r="A1319" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1319" s="2" t="inlineStr">
+      <c r="A1319" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1319" s="3" t="inlineStr">
         <is>
           <t>6009-001476</t>
         </is>
       </c>
-      <c r="C1319" s="2" t="inlineStr">
+      <c r="C1319" s="3" t="inlineStr">
         <is>
           <t>6009-001476</t>
         </is>
       </c>
-      <c r="D1319" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1319" s="2" t="n"/>
-      <c r="F1319" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 6009-001476</t>
-        </is>
-      </c>
-      <c r="G1319" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1319" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1319" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1319" s="3" t="n"/>
+      <c r="F1319" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Dryer Hex Screw - 6009-001476</t>
+        </is>
+      </c>
+      <c r="G1319" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1319" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Image for Samsung Screw Smg6009-001476 from HD Supply | Hex Screw / fits dryer</t>
         </is>
       </c>
     </row>
@@ -52919,40 +52967,40 @@
       </c>
     </row>
     <row r="1334">
-      <c r="A1334" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1334" s="2" t="inlineStr">
+      <c r="A1334" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1334" s="3" t="inlineStr">
         <is>
           <t>6006-001171</t>
         </is>
       </c>
-      <c r="C1334" s="2" t="inlineStr">
+      <c r="C1334" s="3" t="inlineStr">
         <is>
           <t>6006-001171</t>
         </is>
       </c>
-      <c r="D1334" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1334" s="2" t="n"/>
-      <c r="F1334" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 6006-001171</t>
-        </is>
-      </c>
-      <c r="G1334" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1334" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1334" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1334" s="3" t="n"/>
+      <c r="F1334" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Range Screw, Cooking Plate - 6006-001171</t>
+        </is>
+      </c>
+      <c r="G1334" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1334" s="3" t="inlineStr">
+        <is>
+          <t>Site title: samsung 6006 001171 screw cooking plate 13692678 | Screw, cooking plate / fits range</t>
         </is>
       </c>
     </row>
@@ -53931,40 +53979,44 @@
       </c>
     </row>
     <row r="1360">
-      <c r="A1360" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1360" s="2" t="inlineStr">
+      <c r="A1360" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1360" s="3" t="inlineStr">
         <is>
           <t>AH81-09825A</t>
         </is>
       </c>
-      <c r="C1360" s="2" t="inlineStr">
+      <c r="C1360" s="3" t="inlineStr">
         <is>
           <t>ah81-09825a</t>
         </is>
       </c>
-      <c r="D1360" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1360" s="2" t="n"/>
-      <c r="F1360" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-09825A</t>
-        </is>
-      </c>
-      <c r="G1360" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1360" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit (only in collection page summary; no link with PN title)</t>
+      <c r="D1360" s="3" t="inlineStr">
+        <is>
+          <t>Verified (page found)</t>
+        </is>
+      </c>
+      <c r="E1360" s="3" t="inlineStr">
+        <is>
+          <t>https://samsungparts.com/products/ah81-09825a</t>
+        </is>
+      </c>
+      <c r="F1360" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Machine Screw - AH81-09825A</t>
+        </is>
+      </c>
+      <c r="G1360" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1360" s="3" t="inlineStr">
+        <is>
+          <t>Site title: ah81 09825a | A/S-Screw-Machine / fits sound bar</t>
         </is>
       </c>
     </row>
@@ -54045,40 +54097,40 @@
       </c>
     </row>
     <row r="1363">
-      <c r="A1363" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1363" s="2" t="inlineStr">
+      <c r="A1363" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1363" s="3" t="inlineStr">
         <is>
           <t>AA59-00430A</t>
         </is>
       </c>
-      <c r="C1363" s="2" t="inlineStr">
+      <c r="C1363" s="3" t="inlineStr">
         <is>
           <t>aa59-00430a</t>
         </is>
       </c>
-      <c r="D1363" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1363" s="2" t="n"/>
-      <c r="F1363" s="2" t="inlineStr">
-        <is>
-          <t>Samsung AV Replacement Part - AA59-00430A</t>
-        </is>
-      </c>
-      <c r="G1363" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1363" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1363" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1363" s="3" t="n"/>
+      <c r="F1363" s="3" t="inlineStr">
+        <is>
+          <t>Samsung TV Remote Control - AA59-00430A</t>
+        </is>
+      </c>
+      <c r="G1363" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1363" s="3" t="inlineStr">
+        <is>
+          <t>Site title: AA59-00430A Remote Control | Remote Control / fits TV</t>
         </is>
       </c>
     </row>
@@ -55107,40 +55159,40 @@
       </c>
     </row>
     <row r="1390">
-      <c r="A1390" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1390" s="2" t="inlineStr">
+      <c r="A1390" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1390" s="3" t="inlineStr">
         <is>
           <t>3402-000165</t>
         </is>
       </c>
-      <c r="C1390" s="2" t="inlineStr">
+      <c r="C1390" s="3" t="inlineStr">
         <is>
           <t>3402-000165</t>
         </is>
       </c>
-      <c r="D1390" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1390" s="2" t="n"/>
-      <c r="F1390" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 3402-000165</t>
-        </is>
-      </c>
-      <c r="G1390" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1390" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1390" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1390" s="3" t="n"/>
+      <c r="F1390" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Refrigerator Switch, Rocker - 3402-000165</t>
+        </is>
+      </c>
+      <c r="G1390" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1390" s="3" t="inlineStr">
+        <is>
+          <t>Site title: samsung switch rocker 3402 000165 ap4366120 | Switch, Rocker / fits refrigerator</t>
         </is>
       </c>
     </row>
@@ -55419,40 +55471,40 @@
       </c>
     </row>
     <row r="1398">
-      <c r="A1398" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1398" s="2" t="inlineStr">
+      <c r="A1398" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1398" s="3" t="inlineStr">
         <is>
           <t>3701-001819</t>
         </is>
       </c>
-      <c r="C1398" s="2" t="inlineStr">
+      <c r="C1398" s="3" t="inlineStr">
         <is>
           <t>3701-001819</t>
         </is>
       </c>
-      <c r="D1398" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1398" s="2" t="n"/>
-      <c r="F1398" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 3701-001819</t>
-        </is>
-      </c>
-      <c r="G1398" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1398" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1398" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1398" s="3" t="n"/>
+      <c r="F1398" s="3" t="inlineStr">
+        <is>
+          <t>Samsung TV Connecteur-Hdmi (Hdmi Connector) - 3701-001819</t>
+        </is>
+      </c>
+      <c r="G1398" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1398" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 3701-001819 Connecteur-Hdmi | Connecteur-Hdmi (HDMI connector) / fits TV</t>
         </is>
       </c>
     </row>
@@ -58197,40 +58249,40 @@
       </c>
     </row>
     <row r="1469">
-      <c r="A1469" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1469" s="2" t="inlineStr">
+      <c r="A1469" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1469" s="3" t="inlineStr">
         <is>
           <t>1203-007144</t>
         </is>
       </c>
-      <c r="C1469" s="2" t="inlineStr">
+      <c r="C1469" s="3" t="inlineStr">
         <is>
           <t>1203-007144</t>
         </is>
       </c>
-      <c r="D1469" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1469" s="2" t="n"/>
-      <c r="F1469" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 1203-007144</t>
-        </is>
-      </c>
-      <c r="G1469" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1469" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1469" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1469" s="3" t="n"/>
+      <c r="F1469" s="3" t="inlineStr">
+        <is>
+          <t>Samsung TV Ic-Dc/Dc Converter - 1203-007144</t>
+        </is>
+      </c>
+      <c r="G1469" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1469" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 1203-007144 Ic-Dc/Dc Converter | IC-DC/DC Converter / fits TV</t>
         </is>
       </c>
     </row>
@@ -59465,40 +59517,40 @@
       </c>
     </row>
     <row r="1501">
-      <c r="A1501" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1501" s="2" t="inlineStr">
+      <c r="A1501" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1501" s="3" t="inlineStr">
         <is>
           <t>3001-002858</t>
         </is>
       </c>
-      <c r="C1501" s="2" t="inlineStr">
+      <c r="C1501" s="3" t="inlineStr">
         <is>
           <t>3001-002858</t>
         </is>
       </c>
-      <c r="D1501" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1501" s="2" t="n"/>
-      <c r="F1501" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 3001-002858</t>
-        </is>
-      </c>
-      <c r="G1501" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1501" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1501" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1501" s="3" t="n"/>
+      <c r="F1501" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Refrigerator Speaker - 3001-002858</t>
+        </is>
+      </c>
+      <c r="G1501" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1501" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 3001-002858 SPEAKER | Speaker / fits refrigerator</t>
         </is>
       </c>
     </row>
@@ -61365,40 +61417,40 @@
       </c>
     </row>
     <row r="1549">
-      <c r="A1549" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1549" s="2" t="inlineStr">
+      <c r="A1549" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1549" s="3" t="inlineStr">
         <is>
           <t>0609-001204</t>
         </is>
       </c>
-      <c r="C1549" s="2" t="inlineStr">
+      <c r="C1549" s="3" t="inlineStr">
         <is>
           <t>0609-001204</t>
         </is>
       </c>
-      <c r="D1549" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1549" s="2" t="n"/>
-      <c r="F1549" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 0609-001204</t>
-        </is>
-      </c>
-      <c r="G1549" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1549" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1549" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1549" s="3" t="n"/>
+      <c r="F1549" s="3" t="inlineStr">
+        <is>
+          <t>Samsung TV Module Remote Control - 0609-001204</t>
+        </is>
+      </c>
+      <c r="G1549" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1549" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 0609-001204 MODULE REMOTE CONTROL | Module Remote Control / fits TV</t>
         </is>
       </c>
     </row>
@@ -61525,40 +61577,40 @@
       </c>
     </row>
     <row r="1553">
-      <c r="A1553" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1553" s="2" t="inlineStr">
+      <c r="A1553" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1553" s="3" t="inlineStr">
         <is>
           <t>1209-002183</t>
         </is>
       </c>
-      <c r="C1553" s="2" t="inlineStr">
+      <c r="C1553" s="3" t="inlineStr">
         <is>
           <t>1209-002183</t>
         </is>
       </c>
-      <c r="D1553" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1553" s="2" t="n"/>
-      <c r="F1553" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 1209-002183</t>
-        </is>
-      </c>
-      <c r="G1553" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1553" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1553" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1553" s="3" t="n"/>
+      <c r="F1553" s="3" t="inlineStr">
+        <is>
+          <t>Samsung TV Sensor IC - 1209-002183</t>
+        </is>
+      </c>
+      <c r="G1553" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1553" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 1209-002183 IC-SENSOR | IC-Sensor / fits TV</t>
         </is>
       </c>
     </row>

--- a/Samsung_qty_H1_tags.xlsx
+++ b/Samsung_qty_H1_tags.xlsx
@@ -5034,7 +5034,7 @@
       <c r="E116" s="3" t="n"/>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>Samsung Soundbar Samsung Service Jdm-Sub W/F Ps-Wr45Bb|Samsung Parts Usa - AH81-15682A</t>
+          <t>Samsung Soundbar Service Jdm-Sub W/F Ps-Wr45Bb - AH81-15682A</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -6748,7 +6748,7 @@
       <c r="E159" s="3" t="n"/>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Samsung Service Jdm Antenna|Samsung Parts Usa - AH81-13316A</t>
+          <t>Samsung Service Jdm Antenna - AH81-13316A</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -7674,7 +7674,7 @@
       <c r="E182" s="3" t="n"/>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>Samsung Laptop Case Rear|Samsung Parts Usa Assembly - BA98-03232B</t>
+          <t>Samsung Laptop Case Rear Assembly - BA98-03232B</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -12002,7 +12002,7 @@
       <c r="E292" s="3" t="n"/>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>Samsung Laptop Case Rear|Samsung Parts Usa Assembly - BA98-02902A</t>
+          <t>Samsung Laptop Case Rear Assembly - BA98-02902A</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -12836,7 +12836,7 @@
       <c r="E313" s="3" t="n"/>
       <c r="F313" s="3" t="inlineStr">
         <is>
-          <t>Samsung Samsung Service Jdm-Power Module|Samsung Parts Usa - AH81-15334A</t>
+          <t>Samsung Power Module Service Jdm - AH81-15334A</t>
         </is>
       </c>
       <c r="G313" s="3" t="inlineStr">
@@ -13334,7 +13334,7 @@
       <c r="E326" s="3" t="n"/>
       <c r="F326" s="3" t="inlineStr">
         <is>
-          <t>Samsung Laptop Samsung AC Adapter|Samsung Parts Usa - BA44-00298A</t>
+          <t>Samsung Laptop AC Adapter - BA44-00298A</t>
         </is>
       </c>
       <c r="G326" s="3" t="inlineStr">
@@ -13448,7 +13448,7 @@
       <c r="E329" s="3" t="n"/>
       <c r="F329" s="3" t="inlineStr">
         <is>
-          <t>Samsung TV PCB Assembly|Samsung Parts Usa - AH94-03759A</t>
+          <t>Samsung TV PCB Assembly - AH94-03759A</t>
         </is>
       </c>
       <c r="G329" s="3" t="inlineStr">
@@ -19028,7 +19028,7 @@
       <c r="E471" s="3" t="n"/>
       <c r="F471" s="3" t="inlineStr">
         <is>
-          <t>Samsung Samsung OLED Board|Samsung Parts Usa - AH81-15485A</t>
+          <t>Samsung OLED Board - AH81-15485A</t>
         </is>
       </c>
       <c r="G471" s="3" t="inlineStr">
@@ -20360,7 +20360,7 @@
       <c r="E505" s="3" t="n"/>
       <c r="F505" s="3" t="inlineStr">
         <is>
-          <t>Samsung Laptop Adaptor|Samsung Parts Usa - BA44-00353A</t>
+          <t>Samsung Laptop Adaptor - BA44-00353A</t>
         </is>
       </c>
       <c r="G505" s="3" t="inlineStr">
@@ -22462,7 +22462,7 @@
       <c r="E558" s="3" t="n"/>
       <c r="F558" s="3" t="inlineStr">
         <is>
-          <t>Samsung Soundbar Bracket P-Wall|Samsung Parts Usa Assembly - AH96-03944B</t>
+          <t>Samsung Soundbar Wall Bracket P Assembly - AH96-03944B</t>
         </is>
       </c>
       <c r="G558" s="3" t="inlineStr">
@@ -22892,7 +22892,7 @@
       <c r="E569" s="3" t="n"/>
       <c r="F569" s="3" t="inlineStr">
         <is>
-          <t>Samsung Ckd-Remote Control|Samsung Parts Usa - AA83-00654A</t>
+          <t>Samsung Remote Control Ckd - AA83-00654A</t>
         </is>
       </c>
       <c r="G569" s="3" t="inlineStr">
@@ -25404,7 +25404,7 @@
       <c r="E633" s="3" t="n"/>
       <c r="F633" s="3" t="inlineStr">
         <is>
-          <t>Samsung Samsung Service Jdm-Remote Control|Samsung Parts Usa - AH81-14847A</t>
+          <t>Samsung Remote Control Service Jdm - AH81-14847A</t>
         </is>
       </c>
       <c r="G633" s="3" t="inlineStr">
@@ -26104,7 +26104,7 @@
       <c r="E651" s="3" t="n"/>
       <c r="F651" s="3" t="inlineStr">
         <is>
-          <t>Samsung Samsung Service Jdm-Power Cord|Samsung Parts Usa - AH81-14849A</t>
+          <t>Samsung Power Cord Service Jdm - AH81-14849A</t>
         </is>
       </c>
       <c r="G651" s="3" t="inlineStr">

--- a/Samsung_qty_H1_tags.xlsx
+++ b/Samsung_qty_H1_tags.xlsx
@@ -29541,40 +29541,44 @@
       </c>
     </row>
     <row r="739">
-      <c r="A739" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B739" s="2" t="inlineStr">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
         <is>
           <t>BA43-00391A</t>
         </is>
       </c>
-      <c r="C739" s="2" t="inlineStr">
+      <c r="C739" t="inlineStr">
         <is>
           <t>ba43-00391a</t>
         </is>
       </c>
-      <c r="D739" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E739" s="2" t="n"/>
-      <c r="F739" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA43-00391A</t>
-        </is>
-      </c>
-      <c r="G739" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H739" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Verified (page found)</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>https://samsungparts.com/products/ba43-00391a</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Incell Battery Pack - BA43-00391A</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>Site title: Samsung BA43-00391A Incell Battery Pack-P41Gcj-02- | Incell Battery Pack / fits laptop</t>
         </is>
       </c>
     </row>
@@ -30131,40 +30135,40 @@
       </c>
     </row>
     <row r="754">
-      <c r="A754" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B754" s="2" t="inlineStr">
+      <c r="A754" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B754" s="3" t="inlineStr">
         <is>
           <t>BA81-18114A</t>
         </is>
       </c>
-      <c r="C754" s="2" t="inlineStr">
+      <c r="C754" s="3" t="inlineStr">
         <is>
           <t>ba81-18114a</t>
         </is>
       </c>
-      <c r="D754" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E754" s="2" t="n"/>
-      <c r="F754" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA81-18114A</t>
-        </is>
-      </c>
-      <c r="G754" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H754" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D754" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E754" s="3" t="n"/>
+      <c r="F754" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Keyboard - BA81-18114A</t>
+        </is>
+      </c>
+      <c r="G754" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H754" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung BA81-18114A Keyboard|Samsung Parts USA | Keyboard / fits computer</t>
         </is>
       </c>
     </row>
@@ -30839,40 +30843,40 @@
       </c>
     </row>
     <row r="772">
-      <c r="A772" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B772" s="2" t="inlineStr">
+      <c r="A772" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B772" s="3" t="inlineStr">
         <is>
           <t>AH81-15423A</t>
         </is>
       </c>
-      <c r="C772" s="2" t="inlineStr">
+      <c r="C772" s="3" t="inlineStr">
         <is>
           <t>ah81-15423a</t>
         </is>
       </c>
-      <c r="D772" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E772" s="2" t="n"/>
-      <c r="F772" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-15423A</t>
-        </is>
-      </c>
-      <c r="G772" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H772" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D772" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E772" s="3" t="n"/>
+      <c r="F772" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Assembly Kit Main Service Jdm - AH81-15423A</t>
+        </is>
+      </c>
+      <c r="G772" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H772" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung samsung AH81-15423A SERVICE JDM-ASSEMBLY KIT MAIN|Samsung Parts USA | Service JDM-Assembly Kit Main / fits None</t>
         </is>
       </c>
     </row>
@@ -31113,40 +31117,40 @@
       </c>
     </row>
     <row r="779">
-      <c r="A779" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B779" s="2" t="inlineStr">
+      <c r="A779" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B779" s="3" t="inlineStr">
         <is>
           <t>AH94-03877B</t>
         </is>
       </c>
-      <c r="C779" s="2" t="inlineStr">
+      <c r="C779" s="3" t="inlineStr">
         <is>
           <t>ah94-03877b</t>
         </is>
       </c>
-      <c r="D779" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E779" s="2" t="n"/>
-      <c r="F779" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH94-03877B</t>
-        </is>
-      </c>
-      <c r="G779" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H779" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D779" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E779" s="3" t="n"/>
+      <c r="F779" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Assembly PCB Amp Rear Speaker-Right (Amp PCB Assembly) - AH94-03877B</t>
+        </is>
+      </c>
+      <c r="G779" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H779" s="3" t="inlineStr">
+        <is>
+          <t>Site title: samsung AH94-03877B ASSY PCB AMP REAR SPEAKER-RIGH– Samsung Parts USA | ASSY PCB AMP REAR SPEAKER-RIGHT (amp PCB assembly) / fits soundbar/speaker</t>
         </is>
       </c>
     </row>
@@ -32841,40 +32845,40 @@
       </c>
     </row>
     <row r="823">
-      <c r="A823" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B823" s="2" t="inlineStr">
+      <c r="A823" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B823" s="3" t="inlineStr">
         <is>
           <t>AH81-15425A</t>
         </is>
       </c>
-      <c r="C823" s="2" t="inlineStr">
+      <c r="C823" s="3" t="inlineStr">
         <is>
           <t>ah81-15425a</t>
         </is>
       </c>
-      <c r="D823" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E823" s="2" t="n"/>
-      <c r="F823" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-15425A</t>
-        </is>
-      </c>
-      <c r="G823" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H823" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D823" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E823" s="3" t="n"/>
+      <c r="F823" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Assembly Pba Main (Main Board) - AH81-15425A</t>
+        </is>
+      </c>
+      <c r="G823" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H823" s="3" t="inlineStr">
+        <is>
+          <t>Site title: samsung AH81-15425A ASSY PBA MAIN– Samsung Parts USA | ASSY PBA MAIN (main board) / fits soundbar/speaker</t>
         </is>
       </c>
     </row>
@@ -32959,40 +32963,40 @@
       </c>
     </row>
     <row r="826">
-      <c r="A826" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B826" s="2" t="inlineStr">
+      <c r="A826" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B826" s="3" t="inlineStr">
         <is>
           <t>AH82-01198A</t>
         </is>
       </c>
-      <c r="C826" s="2" t="inlineStr">
+      <c r="C826" s="3" t="inlineStr">
         <is>
           <t>ah82-01198a</t>
         </is>
       </c>
-      <c r="D826" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E826" s="2" t="n"/>
-      <c r="F826" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH82-01198A</t>
-        </is>
-      </c>
-      <c r="G826" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H826" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D826" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E826" s="3" t="n"/>
+      <c r="F826" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Assy-Speaker (Speaker Assembly) - AH82-01198A</t>
+        </is>
+      </c>
+      <c r="G826" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H826" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung AH82-01198A A/S ASSY-Speaker | A/S ASSY-Speaker (speaker assembly) / fits None</t>
         </is>
       </c>
     </row>
@@ -35613,40 +35617,40 @@
       </c>
     </row>
     <row r="893">
-      <c r="A893" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B893" s="2" t="inlineStr">
+      <c r="A893" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B893" s="3" t="inlineStr">
         <is>
           <t>6031-001531</t>
         </is>
       </c>
-      <c r="C893" s="2" t="inlineStr">
+      <c r="C893" s="3" t="inlineStr">
         <is>
           <t>6031-001531</t>
         </is>
       </c>
-      <c r="D893" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E893" s="2" t="n"/>
-      <c r="F893" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 6031-001531</t>
-        </is>
-      </c>
-      <c r="G893" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H893" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D893" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E893" s="3" t="n"/>
+      <c r="F893" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Plain Washer - 6031-001531</t>
+        </is>
+      </c>
+      <c r="G893" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H893" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 6031-001531 PLAIN WASHWER– Samsung Parts USA | Plain Washer / fits washing machine</t>
         </is>
       </c>
     </row>
@@ -36191,40 +36195,40 @@
       </c>
     </row>
     <row r="908">
-      <c r="A908" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B908" s="2" t="inlineStr">
+      <c r="A908" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B908" s="3" t="inlineStr">
         <is>
           <t>AH64-05867A</t>
         </is>
       </c>
-      <c r="C908" s="2" t="inlineStr">
+      <c r="C908" s="3" t="inlineStr">
         <is>
           <t>ah64-05867a</t>
         </is>
       </c>
-      <c r="D908" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E908" s="2" t="n"/>
-      <c r="F908" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH64-05867A</t>
-        </is>
-      </c>
-      <c r="G908" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H908" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D908" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E908" s="3" t="n"/>
+      <c r="F908" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Volume Button - AH64-05867A</t>
+        </is>
+      </c>
+      <c r="G908" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H908" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung AH64-05867A Button-Volume|Samsung Parts USA | Button-Volume / fits None</t>
         </is>
       </c>
     </row>
@@ -36869,78 +36873,78 @@
       </c>
     </row>
     <row r="925">
-      <c r="A925" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B925" s="2" t="inlineStr">
+      <c r="A925" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B925" s="3" t="inlineStr">
         <is>
           <t>AH81-11256A</t>
         </is>
       </c>
-      <c r="C925" s="2" t="inlineStr">
+      <c r="C925" s="3" t="inlineStr">
         <is>
           <t>ah81-11256a</t>
         </is>
       </c>
-      <c r="D925" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E925" s="2" t="n"/>
-      <c r="F925" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-11256A</t>
-        </is>
-      </c>
-      <c r="G925" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H925" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D925" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E925" s="3" t="n"/>
+      <c r="F925" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar DC Vss Power Board - AH81-11256A</t>
+        </is>
+      </c>
+      <c r="G925" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H925" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung AH81-11256A A/S-Dc Vss-Power Board– Samsung Parts USA | A/S-DC VSS Power Board / fits speaker/soundbar</t>
         </is>
       </c>
     </row>
     <row r="926">
-      <c r="A926" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B926" s="2" t="inlineStr">
+      <c r="A926" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B926" s="3" t="inlineStr">
         <is>
           <t>AH81-11262A</t>
         </is>
       </c>
-      <c r="C926" s="2" t="inlineStr">
+      <c r="C926" s="3" t="inlineStr">
         <is>
           <t>ah81-11262a</t>
         </is>
       </c>
-      <c r="D926" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E926" s="2" t="n"/>
-      <c r="F926" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-11262A</t>
-        </is>
-      </c>
-      <c r="G926" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H926" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D926" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E926" s="3" t="n"/>
+      <c r="F926" s="3" t="inlineStr">
+        <is>
+          <t>Samsung TV Speaker Right Assembly - AH81-11262A</t>
+        </is>
+      </c>
+      <c r="G926" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H926" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung AH81-11262A A/S-Assy-Speaker Right– Samsung Parts USA | A/S-Assy-Speaker Right / fits TV</t>
         </is>
       </c>
     </row>
@@ -37855,40 +37859,40 @@
       </c>
     </row>
     <row r="950">
-      <c r="A950" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B950" s="2" t="inlineStr">
+      <c r="A950" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B950" s="3" t="inlineStr">
         <is>
           <t>AH96-02267E</t>
         </is>
       </c>
-      <c r="C950" s="2" t="inlineStr">
+      <c r="C950" s="3" t="inlineStr">
         <is>
           <t>ah96-02267e</t>
         </is>
       </c>
-      <c r="D950" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E950" s="2" t="n"/>
-      <c r="F950" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH96-02267E</t>
-        </is>
-      </c>
-      <c r="G950" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H950" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D950" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E950" s="3" t="n"/>
+      <c r="F950" s="3" t="inlineStr">
+        <is>
+          <t>Samsung TV Deck Assembly - AH96-02267E</t>
+        </is>
+      </c>
+      <c r="G950" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H950" s="3" t="inlineStr">
+        <is>
+          <t>Site title: AH96-02267E Deck Assembly– Samsung Parts USA | Deck Assembly / fits TV</t>
         </is>
       </c>
     </row>
@@ -40675,40 +40679,40 @@
       </c>
     </row>
     <row r="1022">
-      <c r="A1022" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1022" s="2" t="inlineStr">
+      <c r="A1022" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1022" s="3" t="inlineStr">
         <is>
           <t>AH81-13844A</t>
         </is>
       </c>
-      <c r="C1022" s="2" t="inlineStr">
+      <c r="C1022" s="3" t="inlineStr">
         <is>
           <t>ah81-13844a</t>
         </is>
       </c>
-      <c r="D1022" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1022" s="2" t="n"/>
-      <c r="F1022" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-13844A</t>
-        </is>
-      </c>
-      <c r="G1022" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1022" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1022" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1022" s="3" t="n"/>
+      <c r="F1022" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Wireless Audio Network - AH81-13844A</t>
+        </is>
+      </c>
+      <c r="G1022" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1022" s="3" t="inlineStr">
+        <is>
+          <t>Site title: samsung AH81-13844A A/S-NETWORK-WIRELESS AUDIO;WSA– Samsung Parts USA | A/S-Network-Wireless Audio;WSA / fits soundbar/speaker</t>
         </is>
       </c>
     </row>
@@ -41759,40 +41763,40 @@
       </c>
     </row>
     <row r="1050">
-      <c r="A1050" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1050" s="2" t="inlineStr">
+      <c r="A1050" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1050" s="3" t="inlineStr">
         <is>
           <t>BA98-02175A</t>
         </is>
       </c>
-      <c r="C1050" s="2" t="inlineStr">
+      <c r="C1050" s="3" t="inlineStr">
         <is>
           <t>ba98-02175a</t>
         </is>
       </c>
-      <c r="D1050" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1050" s="2" t="n"/>
-      <c r="F1050" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Laptop Replacement Part - BA98-02175A</t>
-        </is>
-      </c>
-      <c r="G1050" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1050" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1050" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1050" s="3" t="n"/>
+      <c r="F1050" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Top Case Front Assembly - BA98-02175A</t>
+        </is>
+      </c>
+      <c r="G1050" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1050" s="3" t="inlineStr">
+        <is>
+          <t>Site title: BA98-02175A ASSEMBLY CASE FRONT-TOP;JOAN-1– Samsung Parts USA | Assembly Case Front-Top / fits Chromebook (laptop)</t>
         </is>
       </c>
     </row>
@@ -42383,40 +42387,40 @@
       </c>
     </row>
     <row r="1066">
-      <c r="A1066" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1066" s="2" t="inlineStr">
+      <c r="A1066" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1066" s="3" t="inlineStr">
         <is>
           <t>AH81-11539A</t>
         </is>
       </c>
-      <c r="C1066" s="2" t="inlineStr">
+      <c r="C1066" s="3" t="inlineStr">
         <is>
           <t>ah81-11539a</t>
         </is>
       </c>
-      <c r="D1066" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1066" s="2" t="n"/>
-      <c r="F1066" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-11539A</t>
-        </is>
-      </c>
-      <c r="G1066" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1066" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1066" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1066" s="3" t="n"/>
+      <c r="F1066" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar La Panel - AH81-11539A</t>
+        </is>
+      </c>
+      <c r="G1066" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1066" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung AH81-11539A A/S-LA PANEL;08-0MXT70-LA0S,TO– Samsung Parts USA | A/S-LA Panel / fits soundbar/speaker</t>
         </is>
       </c>
     </row>
@@ -43015,40 +43019,40 @@
       </c>
     </row>
     <row r="1082">
-      <c r="A1082" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1082" s="2" t="inlineStr">
+      <c r="A1082" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1082" s="3" t="inlineStr">
         <is>
           <t>3601-001637</t>
         </is>
       </c>
-      <c r="C1082" s="2" t="inlineStr">
+      <c r="C1082" s="3" t="inlineStr">
         <is>
           <t>3601-001637</t>
         </is>
       </c>
-      <c r="D1082" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1082" s="2" t="n"/>
-      <c r="F1082" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 3601-001637</t>
-        </is>
-      </c>
-      <c r="G1082" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1082" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1082" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1082" s="3" t="n"/>
+      <c r="F1082" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Range Cartridge Fuse - 3601-001637</t>
+        </is>
+      </c>
+      <c r="G1082" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1082" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 3601-001637 FUSE-CARTRIDGE– Samsung Parts USA | Fuse-Cartridge / fits range/oven</t>
         </is>
       </c>
     </row>
@@ -44001,78 +44005,78 @@
       </c>
     </row>
     <row r="1107">
-      <c r="A1107" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1107" s="2" t="inlineStr">
+      <c r="A1107" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1107" s="3" t="inlineStr">
         <is>
           <t>4709-002533</t>
         </is>
       </c>
-      <c r="C1107" s="2" t="inlineStr">
+      <c r="C1107" s="3" t="inlineStr">
         <is>
           <t>4709-002533</t>
         </is>
       </c>
-      <c r="D1107" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1107" s="2" t="n"/>
-      <c r="F1107" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 4709-002533</t>
-        </is>
-      </c>
-      <c r="G1107" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1107" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1107" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1107" s="3" t="n"/>
+      <c r="F1107" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Washer Lan Module W - 4709-002533</t>
+        </is>
+      </c>
+      <c r="G1107" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1107" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 4709-002533 W-LAN MODULE– Samsung Parts USA | W-LAN Module / fits dishwasher</t>
         </is>
       </c>
     </row>
     <row r="1108">
-      <c r="A1108" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1108" s="2" t="inlineStr">
+      <c r="A1108" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1108" s="3" t="inlineStr">
         <is>
           <t>AH94-03807A</t>
         </is>
       </c>
-      <c r="C1108" s="2" t="inlineStr">
+      <c r="C1108" s="3" t="inlineStr">
         <is>
           <t>ah94-03807a</t>
         </is>
       </c>
-      <c r="D1108" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1108" s="2" t="n"/>
-      <c r="F1108" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH94-03807A</t>
-        </is>
-      </c>
-      <c r="G1108" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1108" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1108" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1108" s="3" t="n"/>
+      <c r="F1108" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar PCB Main Assembly - AH94-03807A</t>
+        </is>
+      </c>
+      <c r="G1108" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1108" s="3" t="inlineStr">
+        <is>
+          <t>Site title: AH94-03807A PCB Main Assembly– Samsung Parts USA | PCB Main Assembly / fits soundbar/TV (listing inconsistent)</t>
         </is>
       </c>
     </row>
@@ -44313,40 +44317,40 @@
       </c>
     </row>
     <row r="1115">
-      <c r="A1115" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1115" s="2" t="inlineStr">
+      <c r="A1115" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1115" s="3" t="inlineStr">
         <is>
           <t>AH81-15422A</t>
         </is>
       </c>
-      <c r="C1115" s="2" t="inlineStr">
+      <c r="C1115" s="3" t="inlineStr">
         <is>
           <t>ah81-15422a</t>
         </is>
       </c>
-      <c r="D1115" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1115" s="2" t="n"/>
-      <c r="F1115" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-15422A</t>
-        </is>
-      </c>
-      <c r="G1115" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1115" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1115" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1115" s="3" t="n"/>
+      <c r="F1115" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Soundbar Assembly Spk Sub Service Jdm - AH81-15422A</t>
+        </is>
+      </c>
+      <c r="G1115" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1115" s="3" t="inlineStr">
+        <is>
+          <t>Site title: samsung AH81-15422A SERVICE JDM-ASSEMBLY SPK SUB– Samsung Parts USA | Service JDM-Assembly Spk Sub / fits speaker/soundbar</t>
         </is>
       </c>
     </row>
@@ -45863,78 +45867,78 @@
       </c>
     </row>
     <row r="1154">
-      <c r="A1154" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1154" s="2" t="inlineStr">
+      <c r="A1154" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1154" s="3" t="inlineStr">
         <is>
           <t>AH81-13713A</t>
         </is>
       </c>
-      <c r="C1154" s="2" t="inlineStr">
+      <c r="C1154" s="3" t="inlineStr">
         <is>
           <t>ah81-13713a</t>
         </is>
       </c>
-      <c r="D1154" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1154" s="2" t="n"/>
-      <c r="F1154" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-13713A</t>
-        </is>
-      </c>
-      <c r="G1154" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1154" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1154" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1154" s="3" t="n"/>
+      <c r="F1154" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Wl Wireless Module Service Jdm - AH81-13713A</t>
+        </is>
+      </c>
+      <c r="G1154" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1154" s="3" t="inlineStr">
+        <is>
+          <t>Site title: samsung AH81-13713A SERVICE JDM-WL WIRELESS MODULE– Samsung Parts USA | Service JDM-WL Wireless Module / fits None</t>
         </is>
       </c>
     </row>
     <row r="1155">
-      <c r="A1155" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1155" s="2" t="inlineStr">
+      <c r="A1155" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1155" s="3" t="inlineStr">
         <is>
           <t>AH81-14701A</t>
         </is>
       </c>
-      <c r="C1155" s="2" t="inlineStr">
+      <c r="C1155" s="3" t="inlineStr">
         <is>
           <t>ah81-14701a</t>
         </is>
       </c>
-      <c r="D1155" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1155" s="2" t="n"/>
-      <c r="F1155" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-14701A</t>
-        </is>
-      </c>
-      <c r="G1155" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1155" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1155" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1155" s="3" t="n"/>
+      <c r="F1155" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Service Jdm Pba-Main (Main PCB Assembly) - AH81-14701A</t>
+        </is>
+      </c>
+      <c r="G1155" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1155" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung AH81-14701A Svc Jdm Pba-Main|Samsung Parts USA | Svc Jdm Pba-Main (main PCB assembly) / fits None</t>
         </is>
       </c>
     </row>
@@ -47679,40 +47683,40 @@
       </c>
     </row>
     <row r="1200">
-      <c r="A1200" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1200" s="2" t="inlineStr">
+      <c r="A1200" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1200" s="3" t="inlineStr">
         <is>
           <t>AH83-00496A</t>
         </is>
       </c>
-      <c r="C1200" s="2" t="inlineStr">
+      <c r="C1200" s="3" t="inlineStr">
         <is>
           <t>ah83-00496a</t>
         </is>
       </c>
-      <c r="D1200" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1200" s="2" t="n"/>
-      <c r="F1200" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH83-00496A</t>
-        </is>
-      </c>
-      <c r="G1200" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1200" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1200" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1200" s="3" t="n"/>
+      <c r="F1200" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Speaker Wire Ckd - AH83-00496A</t>
+        </is>
+      </c>
+      <c r="G1200" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1200" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung samsung AH83-00496A CKD-SPEAKER WIRE|Samsung Parts USA | CKD-Speaker Wire / fits None</t>
         </is>
       </c>
     </row>
@@ -48623,40 +48627,40 @@
       </c>
     </row>
     <row r="1224">
-      <c r="A1224" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1224" s="2" t="inlineStr">
+      <c r="A1224" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1224" s="3" t="inlineStr">
         <is>
           <t>AH81-09744A</t>
         </is>
       </c>
-      <c r="C1224" s="2" t="inlineStr">
+      <c r="C1224" s="3" t="inlineStr">
         <is>
           <t>ah81-09744a</t>
         </is>
       </c>
-      <c r="D1224" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1224" s="2" t="n"/>
-      <c r="F1224" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-09744A</t>
-        </is>
-      </c>
-      <c r="G1224" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1224" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1224" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1224" s="3" t="n"/>
+      <c r="F1224" s="3" t="inlineStr">
+        <is>
+          <t>Samsung DC Vss Power Board - AH81-09744A</t>
+        </is>
+      </c>
+      <c r="G1224" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1224" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung AH81-09744A A/S-Dc Vss-Power Board;Tps2100|Samsung Parts USA | A/S-DC VSS Power Board / fits None</t>
         </is>
       </c>
     </row>
@@ -49681,40 +49685,40 @@
       </c>
     </row>
     <row r="1251">
-      <c r="A1251" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1251" s="2" t="inlineStr">
+      <c r="A1251" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1251" s="3" t="inlineStr">
         <is>
           <t>AH39-00540A</t>
         </is>
       </c>
-      <c r="C1251" s="2" t="inlineStr">
+      <c r="C1251" s="3" t="inlineStr">
         <is>
           <t>ah39-00540a</t>
         </is>
       </c>
-      <c r="D1251" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1251" s="2" t="n"/>
-      <c r="F1251" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH39-00540A</t>
-        </is>
-      </c>
-      <c r="G1251" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1251" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1251" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1251" s="3" t="n"/>
+      <c r="F1251" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Cable Interface - AH39-00540A</t>
+        </is>
+      </c>
+      <c r="G1251" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1251" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung AH39-00540A CBF INTERFACE|Samsung Parts USA | CBF Interface / fits None</t>
         </is>
       </c>
     </row>
@@ -51341,40 +51345,40 @@
       </c>
     </row>
     <row r="1293">
-      <c r="A1293" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1293" s="2" t="inlineStr">
+      <c r="A1293" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1293" s="3" t="inlineStr">
         <is>
           <t>4709-002892</t>
         </is>
       </c>
-      <c r="C1293" s="2" t="inlineStr">
+      <c r="C1293" s="3" t="inlineStr">
         <is>
           <t>4709-002892</t>
         </is>
       </c>
-      <c r="D1293" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1293" s="2" t="n"/>
-      <c r="F1293" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 4709-002892</t>
-        </is>
-      </c>
-      <c r="G1293" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1293" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit (only 4709-002829)</t>
+      <c r="D1293" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1293" s="3" t="n"/>
+      <c r="F1293" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Refrigerator W Lan Module - 4709-002892</t>
+        </is>
+      </c>
+      <c r="G1293" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1293" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 4709-002892 W Lan Module– Samsung Parts USA | W Lan Module / fits refrigerator</t>
         </is>
       </c>
     </row>
@@ -52129,40 +52133,40 @@
       </c>
     </row>
     <row r="1313">
-      <c r="A1313" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1313" s="2" t="inlineStr">
+      <c r="A1313" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1313" s="3" t="inlineStr">
         <is>
           <t>7UQ75-40028</t>
         </is>
       </c>
-      <c r="C1313" s="2" t="inlineStr">
+      <c r="C1313" s="3" t="inlineStr">
         <is>
           <t>7uq75-40028</t>
         </is>
       </c>
-      <c r="D1313" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1313" s="2" t="n"/>
-      <c r="F1313" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 7UQ75-40028</t>
-        </is>
-      </c>
-      <c r="G1313" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1313" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1313" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1313" s="3" t="n"/>
+      <c r="F1313" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Cassette - 7UQ75-40028</t>
+        </is>
+      </c>
+      <c r="G1313" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1313" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung 7UQ75-40028 CASSETTE|Samsung Parts USA | Cassette / fits None</t>
         </is>
       </c>
     </row>
@@ -52327,40 +52331,40 @@
       </c>
     </row>
     <row r="1318">
-      <c r="A1318" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1318" s="2" t="inlineStr">
+      <c r="A1318" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1318" s="3" t="inlineStr">
         <is>
           <t>AH81-11487A</t>
         </is>
       </c>
-      <c r="C1318" s="2" t="inlineStr">
+      <c r="C1318" s="3" t="inlineStr">
         <is>
           <t>ah81-11487a</t>
         </is>
       </c>
-      <c r="D1318" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1318" s="2" t="n"/>
-      <c r="F1318" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Soundbar Replacement Part - AH81-11487A</t>
-        </is>
-      </c>
-      <c r="G1318" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1318" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1318" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1318" s="3" t="n"/>
+      <c r="F1318" s="3" t="inlineStr">
+        <is>
+          <t>Samsung A S Aux Board - AH81-11487A</t>
+        </is>
+      </c>
+      <c r="G1318" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1318" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung AH81-11487A A S Aux Board|Samsung Parts USA | A S Aux Board / fits None</t>
         </is>
       </c>
     </row>
@@ -52521,40 +52525,40 @@
       </c>
     </row>
     <row r="1323">
-      <c r="A1323" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1323" s="2" t="inlineStr">
+      <c r="A1323" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1323" s="3" t="inlineStr">
         <is>
           <t>4712-001033</t>
         </is>
       </c>
-      <c r="C1323" s="2" t="inlineStr">
+      <c r="C1323" s="3" t="inlineStr">
         <is>
           <t>4712-001033</t>
         </is>
       </c>
-      <c r="D1323" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1323" s="2" t="n"/>
-      <c r="F1323" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 4712-001033</t>
-        </is>
-      </c>
-      <c r="G1323" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1323" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1323" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1323" s="3" t="n"/>
+      <c r="F1323" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Thermostat - 4712-001033</t>
+        </is>
+      </c>
+      <c r="G1323" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1323" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung 4712-001033 Thermostat|Samsung Parts USA | Thermostat / fits None</t>
         </is>
       </c>
     </row>
@@ -54135,40 +54139,40 @@
       </c>
     </row>
     <row r="1364">
-      <c r="A1364" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1364" s="2" t="inlineStr">
+      <c r="A1364" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1364" s="3" t="inlineStr">
         <is>
           <t>AA59-00599A</t>
         </is>
       </c>
-      <c r="C1364" s="2" t="inlineStr">
+      <c r="C1364" s="3" t="inlineStr">
         <is>
           <t>aa59-00599a</t>
         </is>
       </c>
-      <c r="D1364" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1364" s="2" t="n"/>
-      <c r="F1364" s="2" t="inlineStr">
-        <is>
-          <t>Samsung AV Replacement Part - AA59-00599A</t>
-        </is>
-      </c>
-      <c r="G1364" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1364" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1364" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1364" s="3" t="n"/>
+      <c r="F1364" s="3" t="inlineStr">
+        <is>
+          <t>Samsung TV Remote Control - AA59-00599A</t>
+        </is>
+      </c>
+      <c r="G1364" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1364" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung AA59-00599A TV Remote Control|Samsung Parts USA | TV Remote Control / fits TV</t>
         </is>
       </c>
     </row>
@@ -57579,40 +57583,40 @@
       </c>
     </row>
     <row r="1452">
-      <c r="A1452" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1452" s="2" t="inlineStr">
+      <c r="A1452" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1452" s="3" t="inlineStr">
         <is>
           <t>3701-001905</t>
         </is>
       </c>
-      <c r="C1452" s="2" t="inlineStr">
+      <c r="C1452" s="3" t="inlineStr">
         <is>
           <t>3701-001905</t>
         </is>
       </c>
-      <c r="D1452" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1452" s="2" t="n"/>
-      <c r="F1452" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 3701-001905</t>
-        </is>
-      </c>
-      <c r="G1452" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1452" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1452" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1452" s="3" t="n"/>
+      <c r="F1452" s="3" t="inlineStr">
+        <is>
+          <t>Samsung HDMI Connector - 3701-001905</t>
+        </is>
+      </c>
+      <c r="G1452" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1452" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 3701-001905 CONNECTOR-HDMI– Samsung Parts USA | Connector-HDMI / fits None</t>
         </is>
       </c>
     </row>
@@ -58009,40 +58013,40 @@
       </c>
     </row>
     <row r="1463">
-      <c r="A1463" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1463" s="2" t="inlineStr">
+      <c r="A1463" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1463" s="3" t="inlineStr">
         <is>
           <t>3001-002842</t>
         </is>
       </c>
-      <c r="C1463" s="2" t="inlineStr">
+      <c r="C1463" s="3" t="inlineStr">
         <is>
           <t>3001-002842</t>
         </is>
       </c>
-      <c r="D1463" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1463" s="2" t="n"/>
-      <c r="F1463" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 3001-002842</t>
-        </is>
-      </c>
-      <c r="G1463" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1463" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1463" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1463" s="3" t="n"/>
+      <c r="F1463" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Refrigerator Speaker - 3001-002842</t>
+        </is>
+      </c>
+      <c r="G1463" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1463" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 3001-002842 SPEAKER– Samsung Parts USA | Speaker / fits refrigerator</t>
         </is>
       </c>
     </row>
@@ -59631,40 +59635,40 @@
       </c>
     </row>
     <row r="1504">
-      <c r="A1504" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1504" s="2" t="inlineStr">
+      <c r="A1504" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1504" s="3" t="inlineStr">
         <is>
           <t>3708-003073</t>
         </is>
       </c>
-      <c r="C1504" s="2" t="inlineStr">
+      <c r="C1504" s="3" t="inlineStr">
         <is>
           <t>3708-003073</t>
         </is>
       </c>
-      <c r="D1504" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1504" s="2" t="n"/>
-      <c r="F1504" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 3708-003073</t>
-        </is>
-      </c>
-      <c r="G1504" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1504" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1504" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1504" s="3" t="n"/>
+      <c r="F1504" s="3" t="inlineStr">
+        <is>
+          <t>Samsung TV Connector-Fpc/Ffc/Pic - 3708-003073</t>
+        </is>
+      </c>
+      <c r="G1504" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1504" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 3708-003073 CONNECTOR-FPC/FFC/PIC– Samsung Parts USA | Connector-FPC/FFC/PIC / fits TV</t>
         </is>
       </c>
     </row>
@@ -59909,40 +59913,40 @@
       </c>
     </row>
     <row r="1511">
-      <c r="A1511" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1511" s="2" t="inlineStr">
+      <c r="A1511" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1511" s="3" t="inlineStr">
         <is>
           <t>3705-001191</t>
         </is>
       </c>
-      <c r="C1511" s="2" t="inlineStr">
+      <c r="C1511" s="3" t="inlineStr">
         <is>
           <t>3705-001191</t>
         </is>
       </c>
-      <c r="D1511" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1511" s="2" t="n"/>
-      <c r="F1511" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 3705-001191</t>
-        </is>
-      </c>
-      <c r="G1511" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1511" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1511" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1511" s="3" t="n"/>
+      <c r="F1511" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Coaxial Connector - 3705-001191</t>
+        </is>
+      </c>
+      <c r="G1511" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1511" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 3705-001191 CONNECTOR-COAXIAL– Samsung Parts USA | Connector-Coaxial / fits None</t>
         </is>
       </c>
     </row>
@@ -61025,40 +61029,40 @@
       </c>
     </row>
     <row r="1539">
-      <c r="A1539" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1539" s="2" t="inlineStr">
+      <c r="A1539" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1539" s="3" t="inlineStr">
         <is>
           <t>1205-006618</t>
         </is>
       </c>
-      <c r="C1539" s="2" t="inlineStr">
+      <c r="C1539" s="3" t="inlineStr">
         <is>
           <t>1205-006618</t>
         </is>
       </c>
-      <c r="D1539" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1539" s="2" t="n"/>
-      <c r="F1539" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 1205-006618</t>
-        </is>
-      </c>
-      <c r="G1539" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1539" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1539" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1539" s="3" t="n"/>
+      <c r="F1539" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Ic-Nfc/Rfid - 1205-006618</t>
+        </is>
+      </c>
+      <c r="G1539" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1539" s="3" t="inlineStr">
+        <is>
+          <t>Site title: Samsung 1205-006618 Ic-Nfc/Rfid;Sn220Uuk/B026C0,3.– Samsung Parts USA | IC-NFC/RFID / fits None</t>
         </is>
       </c>
     </row>
@@ -61299,40 +61303,40 @@
       </c>
     </row>
     <row r="1546">
-      <c r="A1546" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B1546" s="2" t="inlineStr">
+      <c r="A1546" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B1546" s="3" t="inlineStr">
         <is>
           <t>0402-001195</t>
         </is>
       </c>
-      <c r="C1546" s="2" t="inlineStr">
+      <c r="C1546" s="3" t="inlineStr">
         <is>
           <t>0402-001195</t>
         </is>
       </c>
-      <c r="D1546" s="2" t="inlineStr">
-        <is>
-          <t>Predicted (page not found by search)</t>
-        </is>
-      </c>
-      <c r="E1546" s="2" t="n"/>
-      <c r="F1546" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - 0402-001195</t>
-        </is>
-      </c>
-      <c r="G1546" s="2" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="H1546" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER: part type not identified; brand/category guessed from part-number prefix only. Replace when a description is available. | searched, no exact hit</t>
+      <c r="D1546" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (found only on another site)</t>
+        </is>
+      </c>
+      <c r="E1546" s="3" t="n"/>
+      <c r="F1546" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Rectifier Diode - 0402-001195</t>
+        </is>
+      </c>
+      <c r="G1546" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H1546" s="3" t="inlineStr">
+        <is>
+          <t>Site title: 0402-001195 Diode-Rectifier, F1T4, 40– Samsung Parts USA | Diode-Rectifier / fits DVD player</t>
         </is>
       </c>
     </row>
